--- a/docs/d/207/inyear.xlsx
+++ b/docs/d/207/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -588,7 +588,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 75 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 73 clubs short</t>
         </is>
       </c>
     </row>
@@ -5148,7 +5148,7 @@
         <v>1</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" s="9" t="n">
         <v>0</v>
@@ -6074,7 +6074,7 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6144,8 +6144,8 @@
       <c r="Y56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z56" s="9" t="n">
-        <v>0</v>
+      <c r="Z56" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA56" s="10" t="n">
         <v>1</v>
@@ -8055,7 +8055,7 @@
         </is>
       </c>
       <c r="P76" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q76" s="9" t="n">
         <v>1</v>
@@ -9857,7 +9857,7 @@
         </is>
       </c>
       <c r="E95" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F95" s="6" t="n">
         <v>10</v>
@@ -9927,8 +9927,8 @@
       <c r="Y95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z95" s="9" t="n">
-        <v>0</v>
+      <c r="Z95" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA95" s="10" t="n">
         <v>1</v>
@@ -14554,10 +14554,10 @@
         </is>
       </c>
       <c r="P143" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q143" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R143" s="9" t="n">
         <v>0</v>
@@ -15687,7 +15687,7 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -15918,7 +15918,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>

--- a/docs/d/207/inyear.xlsx
+++ b/docs/d/207/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/207/inyear.xlsx
+++ b/docs/d/207/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 7 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 73 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 62 clubs short</t>
         </is>
       </c>
     </row>
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="P3" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="9" t="n">
         <v>0</v>
@@ -1515,7 +1515,7 @@
         </is>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>10</v>
@@ -1585,8 +1585,8 @@
       <c r="Y9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z9" s="9" t="n">
-        <v>0</v>
+      <c r="Z9" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA9" s="10" t="n">
         <v>1</v>
@@ -1903,7 +1903,7 @@
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="6" t="n">
         <v>10</v>
@@ -1973,8 +1973,8 @@
       <c r="Y13" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z13" s="9" t="n">
-        <v>0</v>
+      <c r="Z13" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA13" s="10" t="n">
         <v>1</v>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2343,8 +2343,8 @@
       <c r="S17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T17" s="9" t="n">
-        <v>0</v>
+      <c r="T17" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U17" s="9" t="n">
         <v>0</v>
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2652,8 +2652,8 @@
       <c r="Y20" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z20" s="9" t="n">
-        <v>0</v>
+      <c r="Z20" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA20" s="10" t="n">
         <v>1</v>
@@ -2776,7 +2776,7 @@
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" s="6" t="n">
         <v>10</v>
@@ -2846,8 +2846,8 @@
       <c r="Y22" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z22" s="9" t="n">
-        <v>0</v>
+      <c r="Z22" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA22" s="10" t="n">
         <v>1</v>
@@ -3469,13 +3469,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
@@ -3514,7 +3514,7 @@
         <v>0</v>
       </c>
       <c r="V29" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W29" s="9" t="n">
         <v>0</v>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -3989,8 +3989,8 @@
       <c r="R34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S34" s="9" t="n">
-        <v>1</v>
+      <c r="S34" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T34" s="9" t="n">
         <v>0</v>
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5562,8 +5562,8 @@
       <c r="Y50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z50" s="9" t="n">
-        <v>0</v>
+      <c r="Z50" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA50" s="10" t="n">
         <v>1</v>
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -6726,8 +6726,8 @@
       <c r="Y62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z62" s="9" t="n">
-        <v>0</v>
+      <c r="Z62" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA62" s="10" t="n">
         <v>1</v>
@@ -6823,8 +6823,8 @@
       <c r="Y63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z63" s="9" t="n">
-        <v>0</v>
+      <c r="Z63" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA63" s="9" t="n">
         <v>0</v>
@@ -9031,7 +9031,7 @@
         <v>2</v>
       </c>
       <c r="R86" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S86" s="9" t="n">
         <v>0</v>
@@ -9663,7 +9663,7 @@
         </is>
       </c>
       <c r="E93" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F93" s="6" t="n">
         <v>10</v>
@@ -9733,8 +9733,8 @@
       <c r="Y93" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z93" s="9" t="n">
-        <v>0</v>
+      <c r="Z93" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA93" s="10" t="n">
         <v>1</v>
@@ -10536,7 +10536,7 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -10606,8 +10606,8 @@
       <c r="Y102" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z102" s="9" t="n">
-        <v>0</v>
+      <c r="Z102" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA102" s="10" t="n">
         <v>1</v>
@@ -11215,7 +11215,7 @@
         </is>
       </c>
       <c r="E109" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F109" s="6" t="n">
         <v>10</v>
@@ -11285,8 +11285,8 @@
       <c r="Y109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z109" s="9" t="n">
-        <v>0</v>
+      <c r="Z109" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA109" s="10" t="n">
         <v>1</v>
@@ -11667,8 +11667,8 @@
       <c r="W113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X113" s="9" t="n">
-        <v>3</v>
+      <c r="X113" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y113" s="9" t="n">
         <v>0</v>
@@ -12864,7 +12864,7 @@
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -12934,8 +12934,8 @@
       <c r="Y126" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z126" s="9" t="n">
-        <v>0</v>
+      <c r="Z126" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA126" s="10" t="n">
         <v>1</v>
@@ -13972,7 +13972,7 @@
         </is>
       </c>
       <c r="P137" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q137" s="9" t="n">
         <v>0</v>
@@ -14457,7 +14457,7 @@
         </is>
       </c>
       <c r="P142" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q142" s="9" t="n">
         <v>0</v>
@@ -14513,7 +14513,7 @@
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>10</v>
@@ -14527,13 +14527,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
@@ -14574,8 +14574,8 @@
       <c r="V143" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W143" s="9" t="n">
-        <v>3</v>
+      <c r="W143" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X143" s="10" t="n">
         <v>5</v>
@@ -15390,7 +15390,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -15423,7 +15423,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -15456,7 +15456,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -15522,7 +15522,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -15654,7 +15654,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -15720,7 +15720,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -15918,7 +15918,7 @@
         <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -15984,7 +15984,7 @@
         <v>5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -16017,7 +16017,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -16116,7 +16116,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -16248,7 +16248,7 @@
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>

--- a/docs/d/207/inyear.xlsx
+++ b/docs/d/207/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 7 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 62 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 38 clubs short</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="6" t="n">
         <v>10</v>
@@ -906,8 +906,8 @@
       <c r="Y2" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z2" s="9" t="n">
-        <v>0</v>
+      <c r="Z2" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA2" s="10" t="n">
         <v>1</v>
@@ -1030,7 +1030,7 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>10</v>
@@ -1100,8 +1100,8 @@
       <c r="Y4" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z4" s="9" t="n">
-        <v>0</v>
+      <c r="Z4" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA4" s="10" t="n">
         <v>1</v>
@@ -1709,7 +1709,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1779,8 +1779,8 @@
       <c r="Y11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" s="9" t="n">
-        <v>0</v>
+      <c r="Z11" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA11" s="10" t="n">
         <v>1</v>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2167,8 +2167,8 @@
       <c r="Y15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z15" s="9" t="n">
-        <v>0</v>
+      <c r="Z15" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA15" s="10" t="n">
         <v>1</v>
@@ -2194,7 +2194,7 @@
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="6" t="n">
         <v>10</v>
@@ -2264,8 +2264,8 @@
       <c r="Y16" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z16" s="9" t="n">
-        <v>0</v>
+      <c r="Z16" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA16" s="10" t="n">
         <v>1</v>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3137,8 +3137,8 @@
       <c r="Y25" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z25" s="9" t="n">
-        <v>0</v>
+      <c r="Z25" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA25" s="10" t="n">
         <v>1</v>
@@ -3261,7 +3261,7 @@
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" s="6" t="n">
         <v>10</v>
@@ -3331,8 +3331,8 @@
       <c r="Y27" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z27" s="9" t="n">
-        <v>0</v>
+      <c r="Z27" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA27" s="10" t="n">
         <v>1</v>
@@ -3884,7 +3884,7 @@
         </is>
       </c>
       <c r="P33" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q33" s="9" t="n">
         <v>0</v>
@@ -4087,7 +4087,7 @@
         <v>0</v>
       </c>
       <c r="S35" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T35" s="10" t="n">
         <v>1</v>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5174,8 +5174,8 @@
       <c r="Y46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z46" s="9" t="n">
-        <v>0</v>
+      <c r="Z46" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA46" s="10" t="n">
         <v>1</v>
@@ -6268,7 +6268,7 @@
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6282,17 +6282,17 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>3</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>5</v>
+      </c>
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M58" s="8" t="n">
@@ -6326,11 +6326,11 @@
       <c r="U58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V58" s="9" t="n">
-        <v>0</v>
+      <c r="V58" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W58" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X58" s="9" t="n">
         <v>2</v>
@@ -6462,7 +6462,7 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6532,8 +6532,8 @@
       <c r="Y60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z60" s="9" t="n">
-        <v>0</v>
+      <c r="Z60" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA60" s="10" t="n">
         <v>1</v>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" s="6" t="n">
         <v>10</v>
@@ -7017,8 +7017,8 @@
       <c r="Y65" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z65" s="9" t="n">
-        <v>0</v>
+      <c r="Z65" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA65" s="10" t="n">
         <v>1</v>
@@ -7303,7 +7303,7 @@
         <v>0</v>
       </c>
       <c r="X68" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y68" s="9" t="n">
         <v>0</v>
@@ -8079,7 +8079,7 @@
         <v>0</v>
       </c>
       <c r="X76" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y76" s="9" t="n">
         <v>0</v>
@@ -8111,7 +8111,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8155,7 +8155,7 @@
         <v>2</v>
       </c>
       <c r="Q77" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R77" s="9" t="n">
         <v>0</v>
@@ -8181,8 +8181,8 @@
       <c r="Y77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z77" s="9" t="n">
-        <v>0</v>
+      <c r="Z77" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA77" s="10" t="n">
         <v>1</v>
@@ -8467,7 +8467,7 @@
         <v>0</v>
       </c>
       <c r="X80" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y80" s="9" t="n">
         <v>0</v>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -8569,8 +8569,8 @@
       <c r="Y81" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z81" s="9" t="n">
-        <v>0</v>
+      <c r="Z81" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA81" s="10" t="n">
         <v>1</v>
@@ -8596,7 +8596,7 @@
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -8637,10 +8637,10 @@
         </is>
       </c>
       <c r="P82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R82" s="9" t="n">
         <v>0</v>
@@ -8666,8 +8666,8 @@
       <c r="Y82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z82" s="9" t="n">
-        <v>0</v>
+      <c r="Z82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA82" s="10" t="n">
         <v>1</v>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F83" s="6" t="n">
         <v>10</v>
@@ -8763,8 +8763,8 @@
       <c r="Y83" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z83" s="9" t="n">
-        <v>0</v>
+      <c r="Z83" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA83" s="10" t="n">
         <v>1</v>
@@ -8984,7 +8984,7 @@
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -9036,8 +9036,8 @@
       <c r="S86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T86" s="9" t="n">
-        <v>0</v>
+      <c r="T86" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U86" s="9" t="n">
         <v>0</v>
@@ -9954,7 +9954,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10024,8 +10024,8 @@
       <c r="Y96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z96" s="9" t="n">
-        <v>0</v>
+      <c r="Z96" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA96" s="10" t="n">
         <v>1</v>
@@ -10924,7 +10924,7 @@
         </is>
       </c>
       <c r="E106" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F106" s="6" t="n">
         <v>10</v>
@@ -10994,8 +10994,8 @@
       <c r="Y106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z106" s="9" t="n">
-        <v>0</v>
+      <c r="Z106" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA106" s="10" t="n">
         <v>1</v>
@@ -11312,7 +11312,7 @@
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -11382,8 +11382,8 @@
       <c r="Y110" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z110" s="9" t="n">
-        <v>0</v>
+      <c r="Z110" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA110" s="10" t="n">
         <v>1</v>
@@ -12185,7 +12185,7 @@
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12255,8 +12255,8 @@
       <c r="Y119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z119" s="9" t="n">
-        <v>0</v>
+      <c r="Z119" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA119" s="10" t="n">
         <v>1</v>
@@ -12282,7 +12282,7 @@
         </is>
       </c>
       <c r="E120" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F120" s="6" t="n">
         <v>10</v>
@@ -12352,8 +12352,8 @@
       <c r="Y120" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z120" s="9" t="n">
-        <v>0</v>
+      <c r="Z120" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA120" s="10" t="n">
         <v>1</v>
@@ -12767,7 +12767,7 @@
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -12837,8 +12837,8 @@
       <c r="Y125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z125" s="9" t="n">
-        <v>0</v>
+      <c r="Z125" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA125" s="10" t="n">
         <v>1</v>
@@ -13155,7 +13155,7 @@
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13225,8 +13225,8 @@
       <c r="Y129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z129" s="9" t="n">
-        <v>0</v>
+      <c r="Z129" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA129" s="10" t="n">
         <v>1</v>
@@ -13737,7 +13737,7 @@
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -13807,8 +13807,8 @@
       <c r="Y135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z135" s="9" t="n">
-        <v>0</v>
+      <c r="Z135" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA135" s="10" t="n">
         <v>1</v>
@@ -13931,7 +13931,7 @@
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -13971,8 +13971,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P137" s="9" t="n">
-        <v>3</v>
+      <c r="P137" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q137" s="9" t="n">
         <v>0</v>
@@ -14971,8 +14971,8 @@
       <c r="Y147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z147" s="9" t="n">
-        <v>0</v>
+      <c r="Z147" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA147" s="9" t="n">
         <v>0</v>
@@ -14998,7 +14998,7 @@
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F148" s="6" t="n">
         <v>10</v>
@@ -15068,8 +15068,8 @@
       <c r="Y148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z148" s="9" t="n">
-        <v>0</v>
+      <c r="Z148" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA148" s="10" t="n">
         <v>1</v>
@@ -15192,7 +15192,7 @@
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -15235,8 +15235,8 @@
       <c r="P150" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q150" s="9" t="n">
-        <v>1</v>
+      <c r="Q150" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R150" s="9" t="n">
         <v>0</v>
@@ -15357,7 +15357,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -15390,7 +15390,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -15423,7 +15423,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -15489,7 +15489,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -15621,7 +15621,7 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -15720,7 +15720,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>0.5</v>
+        <v>0.83</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -15735,7 +15735,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -15753,7 +15753,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -15819,7 +15819,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -15852,7 +15852,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -15885,7 +15885,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -15951,7 +15951,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -16017,7 +16017,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -16050,7 +16050,7 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -16083,7 +16083,7 @@
         <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -16116,7 +16116,7 @@
         <v>5</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -16149,7 +16149,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -16182,7 +16182,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -16215,7 +16215,7 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -16281,7 +16281,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>

--- a/docs/d/207/inyear.xlsx
+++ b/docs/d/207/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:22 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 7 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 38 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 38 clubs short</t>
         </is>
       </c>
     </row>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L2" s="7" t="inlineStr">
         <is>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         </is>
       </c>
       <c r="E4" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" s="6" t="n">
         <v>10</v>
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>4</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L4" s="7" t="inlineStr">
         <is>
@@ -1088,8 +1088,8 @@
       <c r="U4" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V4" s="9" t="n">
-        <v>0</v>
+      <c r="V4" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W4" s="9" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="6" t="n">
         <v>10</v>
@@ -1141,13 +1141,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -1185,11 +1185,11 @@
       <c r="U5" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="9" t="n">
-        <v>3</v>
+      <c r="V5" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W5" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5" s="9" t="n">
         <v>2</v>
@@ -1238,13 +1238,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1335,17 +1335,17 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L7" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M7" s="8" t="n">
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L8" s="7" t="inlineStr">
         <is>
@@ -1529,13 +1529,13 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L9" s="7" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>0</v>
       </c>
       <c r="V9" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W9" s="9" t="n">
         <v>0</v>
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L10" s="7" t="inlineStr">
         <is>
@@ -1723,13 +1723,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W11" s="9" t="n">
         <v>0</v>
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
@@ -1867,8 +1867,8 @@
       <c r="V12" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W12" s="9" t="n">
-        <v>2</v>
+      <c r="W12" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X12" s="9" t="n">
         <v>2</v>
@@ -1917,17 +1917,17 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L13" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M13" s="8" t="n">
@@ -2014,13 +2014,13 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
         </is>
       </c>
       <c r="E15" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="6" t="n">
         <v>10</v>
@@ -2111,13 +2111,13 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L15" s="7" t="inlineStr">
         <is>
@@ -2155,8 +2155,8 @@
       <c r="U15" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V15" s="9" t="n">
-        <v>3</v>
+      <c r="V15" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W15" s="9" t="n">
         <v>0</v>
@@ -2208,13 +2208,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L16" s="7" t="inlineStr">
         <is>
@@ -2499,13 +2499,13 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L19" s="7" t="inlineStr">
         <is>
@@ -2544,7 +2544,7 @@
         <v>0</v>
       </c>
       <c r="V19" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W19" s="9" t="n">
         <v>0</v>
@@ -2596,13 +2596,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L20" s="7" t="inlineStr">
         <is>
@@ -2693,13 +2693,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L21" s="7" t="inlineStr">
         <is>
@@ -2790,13 +2790,13 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -2970,7 +2970,7 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F24" s="6" t="n">
         <v>10</v>
@@ -2984,13 +2984,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>41</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -3028,11 +3028,11 @@
       <c r="U24" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V24" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" s="9" t="n">
-        <v>0</v>
+      <c r="V24" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W24" s="10" t="n">
+        <v>16</v>
       </c>
       <c r="X24" s="10" t="n">
         <v>7</v>
@@ -3081,17 +3081,17 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L25" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L25" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M25" s="8" t="n">
@@ -3129,7 +3129,7 @@
         <v>4</v>
       </c>
       <c r="W25" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X25" s="10" t="n">
         <v>6</v>
@@ -3275,13 +3275,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>2</v>
+        <v>-4</v>
       </c>
       <c r="L27" s="7" t="inlineStr">
         <is>
@@ -3372,13 +3372,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L28" s="7" t="inlineStr">
         <is>
@@ -3469,13 +3469,13 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>6</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L29" s="7" t="inlineStr">
         <is>
@@ -3566,17 +3566,17 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>39</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-39</v>
+      </c>
+      <c r="L30" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M30" s="8" t="n">
@@ -3663,13 +3663,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L31" s="7" t="inlineStr">
         <is>
@@ -3760,13 +3760,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -3857,13 +3857,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="E34" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F34" s="6" t="n">
         <v>10</v>
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
@@ -3998,8 +3998,8 @@
       <c r="U34" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V34" s="9" t="n">
-        <v>3</v>
+      <c r="V34" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W34" s="9" t="n">
         <v>0</v>
@@ -4051,13 +4051,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L35" s="7" t="inlineStr">
         <is>
@@ -4096,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" s="9" t="n">
         <v>0</v>
@@ -4148,13 +4148,13 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L36" s="7" t="inlineStr">
         <is>
@@ -4245,13 +4245,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
@@ -4439,17 +4439,17 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L39" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M39" s="8" t="n">
@@ -4536,13 +4536,13 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L40" s="7" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L41" s="7" t="inlineStr">
         <is>
@@ -4730,17 +4730,17 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L42" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M42" s="8" t="n">
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
@@ -4872,7 +4872,7 @@
         <v>0</v>
       </c>
       <c r="V43" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W43" s="9" t="n">
         <v>0</v>
@@ -4924,13 +4924,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
@@ -5021,13 +5021,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L45" s="7" t="inlineStr">
         <is>
@@ -5118,13 +5118,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
@@ -5163,7 +5163,7 @@
         <v>0</v>
       </c>
       <c r="V46" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
@@ -5215,13 +5215,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
@@ -5312,17 +5312,17 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L48" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L48" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M48" s="8" t="n">
@@ -5409,17 +5409,17 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L49" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M49" s="8" t="n">
@@ -5551,7 +5551,7 @@
         <v>0</v>
       </c>
       <c r="V50" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W50" s="9" t="n">
         <v>0</v>
@@ -5603,17 +5603,17 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L51" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M51" s="8" t="n">
@@ -5648,7 +5648,7 @@
         <v>0</v>
       </c>
       <c r="V51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W51" s="9" t="n">
         <v>0</v>
@@ -5700,13 +5700,13 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L52" s="7" t="inlineStr">
         <is>
@@ -5797,13 +5797,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -5894,13 +5894,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -5991,13 +5991,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6088,17 +6088,17 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L56" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M56" s="8" t="n">
@@ -6185,17 +6185,17 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J57" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L57" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L57" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M57" s="8" t="n">
@@ -6282,17 +6282,17 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>3</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L58" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L58" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M58" s="8" t="n">
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
@@ -6573,17 +6573,17 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L61" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L61" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M61" s="8" t="n">
@@ -6670,13 +6670,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -6715,7 +6715,7 @@
         <v>0</v>
       </c>
       <c r="V62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W62" s="9" t="n">
         <v>0</v>
@@ -6864,13 +6864,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -7058,17 +7058,17 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L66" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M66" s="8" t="n">
@@ -7155,17 +7155,17 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-27</v>
+      </c>
+      <c r="L67" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M67" s="8" t="n">
@@ -7252,13 +7252,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
@@ -7349,13 +7349,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L69" s="7" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>0</v>
       </c>
       <c r="V69" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W69" s="9" t="n">
         <v>0</v>
@@ -7446,13 +7446,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>45</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
         <v>0</v>
       </c>
       <c r="V70" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W70" s="9" t="n">
         <v>0</v>
@@ -7543,13 +7543,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L71" s="7" t="inlineStr">
         <is>
@@ -7640,13 +7640,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         </is>
       </c>
       <c r="P72" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q72" s="9" t="n">
         <v>0</v>
@@ -7737,13 +7737,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -7834,13 +7834,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="L74" s="7" t="inlineStr">
         <is>
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -8028,13 +8028,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
@@ -8125,13 +8125,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
@@ -8222,13 +8222,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>0</v>
+        <v>-11</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8319,13 +8319,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J79" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
@@ -8416,13 +8416,13 @@
         </is>
       </c>
       <c r="I80" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J80" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8443,10 +8443,10 @@
         </is>
       </c>
       <c r="P80" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R80" s="9" t="n">
         <v>0</v>
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -8610,13 +8610,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>0</v>
       </c>
       <c r="V82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W82" s="9" t="n">
         <v>0</v>
@@ -8707,13 +8707,13 @@
         </is>
       </c>
       <c r="I83" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J83" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J84" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>0</v>
+        <v>-12</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -8901,13 +8901,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -8998,13 +8998,13 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J86" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>0</v>
       </c>
       <c r="V86" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W86" s="9" t="n">
         <v>0</v>
@@ -9095,13 +9095,13 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J87" s="4" t="n">
         <v>2</v>
       </c>
       <c r="K87" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
@@ -9192,17 +9192,17 @@
         </is>
       </c>
       <c r="I88" s="4" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J88" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K88" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L88" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L88" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M88" s="8" t="n">
@@ -9240,7 +9240,7 @@
         <v>4</v>
       </c>
       <c r="W88" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X88" s="10" t="n">
         <v>6</v>
@@ -9289,17 +9289,17 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L89" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L89" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M89" s="8" t="n">
@@ -9337,7 +9337,7 @@
         <v>4</v>
       </c>
       <c r="W89" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X89" s="10" t="n">
         <v>7</v>
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="J90" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         <v>0</v>
       </c>
       <c r="V90" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W90" s="9" t="n">
         <v>0</v>
@@ -9483,13 +9483,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J91" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -9580,13 +9580,13 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J92" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K92" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L92" s="7" t="inlineStr">
         <is>
@@ -9677,13 +9677,13 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J93" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K93" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L93" s="7" t="inlineStr">
         <is>
@@ -9774,13 +9774,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J94" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -9819,7 +9819,7 @@
         <v>0</v>
       </c>
       <c r="V94" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W94" s="9" t="n">
         <v>0</v>
@@ -9871,13 +9871,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J95" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
         <v>0</v>
       </c>
       <c r="V95" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W95" s="9" t="n">
         <v>0</v>
@@ -9954,7 +9954,7 @@
         </is>
       </c>
       <c r="E96" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F96" s="6" t="n">
         <v>10</v>
@@ -10012,8 +10012,8 @@
       <c r="U96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V96" s="9" t="n">
-        <v>0</v>
+      <c r="V96" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W96" s="9" t="n">
         <v>0</v>
@@ -10065,17 +10065,17 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="J97" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-14</v>
+      </c>
+      <c r="L97" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M97" s="8" t="n">
@@ -10162,17 +10162,17 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-23</v>
+      </c>
+      <c r="L98" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M98" s="8" t="n">
@@ -10259,17 +10259,17 @@
         </is>
       </c>
       <c r="I99" s="4" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="J99" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-27</v>
+      </c>
+      <c r="L99" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M99" s="8" t="n">
@@ -10356,17 +10356,17 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J100" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L100" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M100" s="8" t="n">
@@ -10401,7 +10401,7 @@
         <v>0</v>
       </c>
       <c r="V100" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J101" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -10480,7 +10480,7 @@
         </is>
       </c>
       <c r="P101" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q101" s="9" t="n">
         <v>0</v>
@@ -10550,13 +10550,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J102" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -10647,13 +10647,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -10744,13 +10744,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J104" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K104" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
@@ -10841,13 +10841,13 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="J105" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K105" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L105" s="7" t="inlineStr">
         <is>
@@ -10938,13 +10938,13 @@
         </is>
       </c>
       <c r="I106" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J106" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -11021,7 +11021,7 @@
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11035,13 +11035,13 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="J107" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>2</v>
+        <v>-10</v>
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
@@ -11070,8 +11070,8 @@
       <c r="R107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S107" s="9" t="n">
-        <v>1</v>
+      <c r="S107" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T107" s="10" t="n">
         <v>1</v>
@@ -11080,7 +11080,7 @@
         <v>2</v>
       </c>
       <c r="V107" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W107" s="9" t="n">
         <v>0</v>
@@ -11132,13 +11132,13 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J108" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
@@ -11229,13 +11229,13 @@
         </is>
       </c>
       <c r="I109" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J109" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
@@ -11371,7 +11371,7 @@
         <v>0</v>
       </c>
       <c r="V110" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W110" s="9" t="n">
         <v>0</v>
@@ -11423,13 +11423,13 @@
         </is>
       </c>
       <c r="I111" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J111" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
@@ -11520,13 +11520,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J112" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L112" s="7" t="inlineStr">
         <is>
@@ -11565,7 +11565,7 @@
         <v>0</v>
       </c>
       <c r="V112" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W112" s="9" t="n">
         <v>0</v>
@@ -11617,17 +11617,17 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L113" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-12</v>
+      </c>
+      <c r="L113" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M113" s="8" t="n">
@@ -11662,7 +11662,7 @@
         <v>0</v>
       </c>
       <c r="V113" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
@@ -11714,13 +11714,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -11811,13 +11811,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>0</v>
       </c>
       <c r="V115" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
@@ -11908,13 +11908,13 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J116" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K116" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L116" s="7" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>0</v>
       </c>
       <c r="V116" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
@@ -12005,13 +12005,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J117" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -12102,17 +12102,17 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L118" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L118" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M118" s="8" t="n">
@@ -12199,13 +12199,13 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J119" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K119" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
@@ -12296,13 +12296,13 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J120" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K120" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
@@ -12393,13 +12393,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J121" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
@@ -12490,13 +12490,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J122" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -12587,13 +12587,13 @@
         </is>
       </c>
       <c r="I123" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J123" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
@@ -12684,13 +12684,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -12878,13 +12878,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J126" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L126" s="7" t="inlineStr">
         <is>
@@ -13072,13 +13072,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J128" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L128" s="7" t="inlineStr">
         <is>
@@ -13117,7 +13117,7 @@
         <v>0</v>
       </c>
       <c r="V128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W128" s="9" t="n">
         <v>0</v>
@@ -13169,13 +13169,13 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J129" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K129" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
@@ -13266,13 +13266,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J130" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L130" s="7" t="inlineStr">
         <is>
@@ -13311,7 +13311,7 @@
         <v>0</v>
       </c>
       <c r="V130" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W130" s="9" t="n">
         <v>0</v>
@@ -13363,13 +13363,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J131" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>0</v>
       </c>
       <c r="V131" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W131" s="9" t="n">
         <v>0</v>
@@ -13460,13 +13460,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J132" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -13543,7 +13543,7 @@
         </is>
       </c>
       <c r="E133" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F133" s="6" t="n">
         <v>10</v>
@@ -13557,17 +13557,17 @@
         </is>
       </c>
       <c r="I133" s="4" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="J133" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L133" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L133" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M133" s="8" t="n">
@@ -13601,11 +13601,11 @@
       <c r="U133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V133" s="9" t="n">
-        <v>3</v>
+      <c r="V133" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W133" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X133" s="10" t="n">
         <v>7</v>
@@ -13654,17 +13654,17 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L134" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L134" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M134" s="8" t="n">
@@ -13699,7 +13699,7 @@
         <v>0</v>
       </c>
       <c r="V134" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W134" s="9" t="n">
         <v>0</v>
@@ -13751,13 +13751,13 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J135" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K135" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L135" s="7" t="inlineStr">
         <is>
@@ -13834,7 +13834,7 @@
         </is>
       </c>
       <c r="E136" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F136" s="6" t="n">
         <v>10</v>
@@ -13848,13 +13848,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L136" s="7" t="inlineStr">
         <is>
@@ -13892,8 +13892,8 @@
       <c r="U136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V136" s="9" t="n">
-        <v>2</v>
+      <c r="V136" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W136" s="9" t="n">
         <v>0</v>
@@ -13945,13 +13945,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>4</v>
+        <v>-9</v>
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>4</v>
       </c>
       <c r="W137" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X137" s="10" t="n">
         <v>6</v>
@@ -14042,13 +14042,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L138" s="7" t="inlineStr">
         <is>
@@ -14236,13 +14236,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J140" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -14266,7 +14266,7 @@
         <v>1</v>
       </c>
       <c r="Q140" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R140" s="9" t="n">
         <v>0</v>
@@ -14281,7 +14281,7 @@
         <v>0</v>
       </c>
       <c r="V140" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W140" s="9" t="n">
         <v>0</v>
@@ -14333,13 +14333,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
@@ -14363,7 +14363,7 @@
         <v>0</v>
       </c>
       <c r="Q141" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R141" s="9" t="n">
         <v>0</v>
@@ -14430,13 +14430,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="J142" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L142" s="7" t="inlineStr">
         <is>
@@ -14527,13 +14527,13 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="J143" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>9</v>
+        <v>-1</v>
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
@@ -14575,7 +14575,7 @@
         <v>4</v>
       </c>
       <c r="W143" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X143" s="10" t="n">
         <v>5</v>
@@ -14624,13 +14624,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="J144" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>4</v>
+        <v>-7</v>
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
@@ -14721,13 +14721,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L145" s="7" t="inlineStr">
         <is>
@@ -14818,13 +14818,13 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J146" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>5</v>
+        <v>-7</v>
       </c>
       <c r="L146" s="4" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>4</v>
       </c>
       <c r="W146" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X146" s="10" t="n">
         <v>5</v>
@@ -14915,13 +14915,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L147" s="7" t="inlineStr">
         <is>
@@ -14960,7 +14960,7 @@
         <v>0</v>
       </c>
       <c r="V147" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W147" s="9" t="n">
         <v>0</v>
@@ -15012,13 +15012,13 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J148" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L148" s="7" t="inlineStr">
         <is>
@@ -15057,7 +15057,7 @@
         <v>0</v>
       </c>
       <c r="V148" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W148" s="9" t="n">
         <v>0</v>
@@ -15095,7 +15095,7 @@
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F149" s="6" t="n">
         <v>10</v>
@@ -15109,13 +15109,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="J149" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>3</v>
+        <v>-2</v>
       </c>
       <c r="L149" s="7" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         </is>
       </c>
       <c r="P149" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q149" s="9" t="n">
         <v>0</v>
@@ -15153,11 +15153,11 @@
       <c r="U149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V149" s="9" t="n">
-        <v>3</v>
+      <c r="V149" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W149" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X149" s="10" t="n">
         <v>6</v>
@@ -15206,13 +15206,13 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J150" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         </is>
       </c>
       <c r="P150" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q150" s="10" t="n">
         <v>2</v>
@@ -15357,7 +15357,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -15390,7 +15390,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -15405,7 +15405,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -15423,7 +15423,7 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -15438,7 +15438,7 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -15489,7 +15489,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -15504,7 +15504,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -15522,7 +15522,7 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -15537,7 +15537,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -15570,7 +15570,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -15603,7 +15603,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -15636,7 +15636,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -15669,7 +15669,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -15702,7 +15702,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -15735,7 +15735,7 @@
         <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -15768,7 +15768,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -15900,7 +15900,7 @@
         <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -15951,7 +15951,7 @@
         <v>4</v>
       </c>
       <c r="D20" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -15966,7 +15966,7 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -15999,7 +15999,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -16017,7 +16017,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -16065,7 +16065,7 @@
         <v>1</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -16098,7 +16098,7 @@
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -16182,7 +16182,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -16197,7 +16197,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -16281,7 +16281,7 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>

--- a/docs/d/207/inyear.xlsx
+++ b/docs/d/207/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/207/inyear.xlsx
+++ b/docs/d/207/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:38 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/207/inyear.xlsx
+++ b/docs/d/207/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/207/inyear.xlsx
+++ b/docs/d/207/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/207/inyear.xlsx
+++ b/docs/d/207/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AA$151</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 7 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 8 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 38 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 38 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA150"/>
+  <dimension ref="A1:AA151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" s="7" t="inlineStr">
         <is>
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="P3" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q3" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R3" s="9" t="n">
         <v>0</v>
@@ -992,7 +992,7 @@
         <v>0</v>
       </c>
       <c r="V3" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W3" s="9" t="n">
         <v>0</v>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>10</v>
@@ -1335,17 +1335,17 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-2</v>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M7" s="8" t="n">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="P7" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q7" s="9" t="n">
         <v>1</v>
@@ -1379,8 +1379,8 @@
       <c r="U7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V7" s="9" t="n">
-        <v>3</v>
+      <c r="V7" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W7" s="9" t="n">
         <v>0</v>
@@ -1723,13 +1723,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="L11" s="7" t="inlineStr">
         <is>
@@ -1806,7 +1806,7 @@
         </is>
       </c>
       <c r="E12" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F12" s="6" t="n">
         <v>10</v>
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
@@ -1861,14 +1861,14 @@
       <c r="T12" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U12" s="9" t="n">
-        <v>0</v>
+      <c r="U12" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V12" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W12" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X12" s="9" t="n">
         <v>2</v>
@@ -1917,13 +1917,13 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="L13" s="7" t="inlineStr">
         <is>
@@ -2305,13 +2305,13 @@
         </is>
       </c>
       <c r="I17" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J17" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="7" t="inlineStr">
         <is>
@@ -2350,7 +2350,7 @@
         <v>0</v>
       </c>
       <c r="V17" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W17" s="9" t="n">
         <v>0</v>
@@ -2887,13 +2887,13 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -3084,10 +3084,10 @@
         <v>16</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="L25" s="7" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         </is>
       </c>
       <c r="P27" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27" s="9" t="n">
         <v>0</v>
@@ -3760,13 +3760,13 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L32" s="7" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>0</v>
       </c>
       <c r="V32" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W32" s="9" t="n">
         <v>0</v>
@@ -3887,7 +3887,7 @@
         <v>1</v>
       </c>
       <c r="Q33" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" s="9" t="n">
         <v>0</v>
@@ -4999,15 +4999,15 @@
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>2714463</v>
+        <v>775</v>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Find Your Voice</t>
+          <t>Astoria Toastmasters</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5021,58 +5021,58 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J45" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M45" s="8" t="n">
+        <v>46387</v>
+      </c>
+      <c r="N45" s="4" t="inlineStr">
+        <is>
+          <t>Officer list on time</t>
+        </is>
+      </c>
+      <c r="O45" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W45" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="K45" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L45" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M45" s="8" t="n">
-        <v>46446</v>
-      </c>
-      <c r="N45" s="4" t="inlineStr">
-        <is>
-          <t>Officers trained Nov-Feb</t>
-        </is>
-      </c>
-      <c r="O45" s="7" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P45" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="W45" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" s="10" t="n">
-        <v>6</v>
+      <c r="X45" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y45" s="9" t="n">
         <v>0</v>
@@ -5080,8 +5080,8 @@
       <c r="Z45" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA45" s="10" t="n">
-        <v>1</v>
+      <c r="AA45" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -5096,11 +5096,11 @@
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>3756318</v>
+        <v>2714463</v>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Nano-Mated Speakers</t>
+          <t>Find Your Voice</t>
         </is>
       </c>
       <c r="E46" s="5" t="n">
@@ -5118,13 +5118,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J46" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
@@ -5145,10 +5145,10 @@
         </is>
       </c>
       <c r="P46" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q46" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" s="9" t="n">
         <v>0</v>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="V46" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X46" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y46" s="9" t="n">
         <v>0</v>
@@ -5193,15 +5193,15 @@
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>7209661</v>
+        <v>3756318</v>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Speak To Lead Toastmasters</t>
+          <t>Nano-Mated Speakers</t>
         </is>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" s="6" t="n">
         <v>10</v>
@@ -5215,13 +5215,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="J47" s="4" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="L47" s="7" t="inlineStr">
         <is>
@@ -5242,37 +5242,37 @@
         </is>
       </c>
       <c r="P47" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q47" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q47" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R47" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T47" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="W47" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X47" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y47" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z47" s="9" t="n">
-        <v>0</v>
+      <c r="Z47" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA47" s="10" t="n">
         <v>1</v>
@@ -5290,11 +5290,11 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>28679467</v>
+        <v>7209661</v>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>The cGMP Communicators</t>
+          <t>Speak To Lead Toastmasters</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
@@ -5312,13 +5312,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>-15</v>
+        <v>-3</v>
       </c>
       <c r="L48" s="7" t="inlineStr">
         <is>
@@ -5339,16 +5339,16 @@
         </is>
       </c>
       <c r="P48" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T48" s="9" t="n">
         <v>0</v>
@@ -5357,13 +5357,13 @@
         <v>0</v>
       </c>
       <c r="V48" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X48" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y48" s="9" t="n">
         <v>0</v>
@@ -5383,19 +5383,19 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>3797086</v>
+        <v>28679467</v>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Sporty Speakers</t>
+          <t>The cGMP Communicators</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>-1</v>
+        <v>-15</v>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
@@ -5439,13 +5439,13 @@
         <v>0</v>
       </c>
       <c r="Q49" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S49" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T49" s="9" t="n">
         <v>0</v>
@@ -5454,7 +5454,7 @@
         <v>0</v>
       </c>
       <c r="V49" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W49" s="9" t="n">
         <v>0</v>
@@ -5465,8 +5465,8 @@
       <c r="Y49" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z49" s="10" t="n">
-        <v>1</v>
+      <c r="Z49" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA49" s="10" t="n">
         <v>1</v>
@@ -5484,11 +5484,11 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>4649162</v>
+        <v>3797086</v>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Storymasters Toastmasters</t>
+          <t>Sporty Speakers</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
@@ -5506,13 +5506,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L50" s="7" t="inlineStr">
         <is>
@@ -5536,13 +5536,13 @@
         <v>0</v>
       </c>
       <c r="Q50" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R50" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S50" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T50" s="9" t="n">
         <v>0</v>
@@ -5557,7 +5557,7 @@
         <v>0</v>
       </c>
       <c r="X50" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y50" s="9" t="n">
         <v>0</v>
@@ -5581,11 +5581,11 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>6869</v>
+        <v>4649162</v>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Tell Me A Story</t>
+          <t>Storymasters Toastmasters</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
@@ -5603,13 +5603,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="L51" s="7" t="inlineStr">
         <is>
@@ -5630,31 +5630,31 @@
         </is>
       </c>
       <c r="P51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q51" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="R51" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T51" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" s="9" t="n">
-        <v>1</v>
-      </c>
       <c r="W51" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X51" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y51" s="9" t="n">
         <v>0</v>
@@ -5678,15 +5678,15 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>7499</v>
+        <v>6869</v>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Tualatin Valley Toastmasters Club</t>
+          <t>Tell Me A Story</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -5700,10 +5700,10 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K52" s="4" t="n">
         <v>-3</v>
@@ -5727,16 +5727,16 @@
         </is>
       </c>
       <c r="P52" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q52" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R52" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S52" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T52" s="9" t="n">
         <v>0</v>
@@ -5745,19 +5745,19 @@
         <v>0</v>
       </c>
       <c r="V52" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W52" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X52" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z52" s="9" t="n">
-        <v>0</v>
+      <c r="Z52" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA52" s="10" t="n">
         <v>1</v>
@@ -5775,15 +5775,15 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>866853</v>
+        <v>7499</v>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Walker Talkers Toastmasters Club</t>
+          <t>Tualatin Valley Toastmasters Club</t>
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -5797,13 +5797,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L53" s="7" t="inlineStr">
         <is>
@@ -5835,14 +5835,14 @@
       <c r="S53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T53" s="10" t="n">
-        <v>1</v>
+      <c r="T53" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U53" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V53" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W53" s="9" t="n">
         <v>0</v>
@@ -5853,8 +5853,8 @@
       <c r="Y53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z53" s="10" t="n">
-        <v>1</v>
+      <c r="Z53" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA53" s="10" t="n">
         <v>1</v>
@@ -5868,19 +5868,19 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>751</v>
+        <v>866853</v>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Cedar Hills Club</t>
+          <t>Walker Talkers Toastmasters Club</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -5894,13 +5894,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J54" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="L54" s="7" t="inlineStr">
         <is>
@@ -5921,10 +5921,10 @@
         </is>
       </c>
       <c r="P54" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q54" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R54" s="9" t="n">
         <v>0</v>
@@ -5932,14 +5932,14 @@
       <c r="S54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T54" s="9" t="n">
-        <v>0</v>
+      <c r="T54" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U54" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V54" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W54" s="9" t="n">
         <v>0</v>
@@ -5969,11 +5969,11 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>2039</v>
+        <v>751</v>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Masterful Presenters</t>
+          <t>Cedar Hills Club</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
@@ -5991,13 +5991,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L55" s="7" t="inlineStr">
         <is>
@@ -6018,10 +6018,10 @@
         </is>
       </c>
       <c r="P55" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q55" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R55" s="9" t="n">
         <v>0</v>
@@ -6066,11 +6066,11 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>28678478</v>
+        <v>2039</v>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>MKS Precision Persuaders</t>
+          <t>Masterful Presenters</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
@@ -6088,13 +6088,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="L56" s="7" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         </is>
       </c>
       <c r="P56" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q56" s="9" t="n">
         <v>0</v>
@@ -6124,7 +6124,7 @@
         <v>0</v>
       </c>
       <c r="S56" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T56" s="9" t="n">
         <v>0</v>
@@ -6133,13 +6133,13 @@
         <v>0</v>
       </c>
       <c r="V56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X56" s="9" t="n">
-        <v>2</v>
+      <c r="X56" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y56" s="9" t="n">
         <v>0</v>
@@ -6163,15 +6163,15 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>6129</v>
+        <v>28678478</v>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>West Beaverton Club</t>
+          <t>MKS Precision Persuaders</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6185,13 +6185,13 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="L57" s="7" t="inlineStr">
         <is>
@@ -6212,7 +6212,7 @@
         </is>
       </c>
       <c r="P57" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q57" s="9" t="n">
         <v>0</v>
@@ -6221,22 +6221,22 @@
         <v>0</v>
       </c>
       <c r="S57" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U57" s="10" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T57" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V57" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X57" s="10" t="n">
-        <v>6</v>
+      <c r="X57" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y57" s="9" t="n">
         <v>0</v>
@@ -6256,19 +6256,19 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>622</v>
+        <v>6129</v>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Chanticleers Toastmasters Club</t>
+          <t>West Beaverton Club</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6282,13 +6282,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6309,7 +6309,7 @@
         </is>
       </c>
       <c r="P58" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q58" s="9" t="n">
         <v>0</v>
@@ -6320,26 +6320,26 @@
       <c r="S58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T58" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V58" s="10" t="n">
-        <v>4</v>
+      <c r="T58" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V58" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="W58" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X58" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="X58" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z58" s="9" t="n">
-        <v>0</v>
+      <c r="Z58" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA58" s="10" t="n">
         <v>1</v>
@@ -6357,11 +6357,11 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>9459</v>
+        <v>622</v>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Feedbackers Toastmasters Club</t>
+          <t>Chanticleers Toastmasters Club</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
@@ -6379,13 +6379,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L59" s="7" t="inlineStr">
         <is>
@@ -6423,20 +6423,20 @@
       <c r="U59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V59" s="9" t="n">
-        <v>1</v>
+      <c r="V59" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W59" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X59" s="10" t="n">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="X59" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y59" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z59" s="10" t="n">
-        <v>1</v>
+      <c r="Z59" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA59" s="10" t="n">
         <v>1</v>
@@ -6454,11 +6454,11 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>1451910</v>
+        <v>9459</v>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Liberty Talkers</t>
+          <t>Feedbackers Toastmasters Club</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
@@ -6479,10 +6479,10 @@
         <v>8</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L60" s="7" t="inlineStr">
         <is>
@@ -6551,11 +6551,11 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>9579</v>
+        <v>1451910</v>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Silicon Forest Club</t>
+          <t>Liberty Talkers</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
@@ -6573,13 +6573,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>-3</v>
+        <v>1</v>
       </c>
       <c r="L61" s="7" t="inlineStr">
         <is>
@@ -6603,7 +6603,7 @@
         <v>0</v>
       </c>
       <c r="Q61" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R61" s="9" t="n">
         <v>0</v>
@@ -6618,7 +6618,7 @@
         <v>0</v>
       </c>
       <c r="V61" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W61" s="9" t="n">
         <v>0</v>
@@ -6648,15 +6648,15 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>4421</v>
+        <v>9579</v>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Timber Talkers</t>
+          <t>Silicon Forest Club</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -6670,13 +6670,13 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="L62" s="7" t="inlineStr">
         <is>
@@ -6700,28 +6700,28 @@
         <v>0</v>
       </c>
       <c r="Q62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R62" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S62" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T62" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T62" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V62" s="9" t="n">
-        <v>1</v>
+      <c r="V62" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W62" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X62" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y62" s="9" t="n">
         <v>0</v>
@@ -6745,15 +6745,15 @@
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>1216392</v>
+        <v>4421</v>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Wake Up, Beaverton! Toastmasters</t>
+          <t>Timber Talkers</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" s="6" t="n">
         <v>10</v>
@@ -6767,13 +6767,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J63" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L63" s="7" t="inlineStr">
         <is>
@@ -6781,11 +6781,11 @@
         </is>
       </c>
       <c r="M63" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N63" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O63" s="7" t="inlineStr">
@@ -6797,7 +6797,7 @@
         <v>0</v>
       </c>
       <c r="Q63" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R63" s="9" t="n">
         <v>0</v>
@@ -6812,7 +6812,7 @@
         <v>0</v>
       </c>
       <c r="V63" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W63" s="9" t="n">
         <v>0</v>
@@ -6826,8 +6826,8 @@
       <c r="Z63" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA63" s="9" t="n">
-        <v>0</v>
+      <c r="AA63" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -6838,19 +6838,19 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>87</v>
+        <v>1216392</v>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>AAA Towsters</t>
+          <t>Wake Up, Beaverton! Toastmasters</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -6864,13 +6864,13 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L64" s="7" t="inlineStr">
         <is>
@@ -6878,11 +6878,11 @@
         </is>
       </c>
       <c r="M64" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O64" s="7" t="inlineStr">
@@ -6894,13 +6894,13 @@
         <v>0</v>
       </c>
       <c r="Q64" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R64" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S64" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T64" s="9" t="n">
         <v>0</v>
@@ -6909,13 +6909,13 @@
         <v>0</v>
       </c>
       <c r="V64" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W64" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X64" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y64" s="9" t="n">
         <v>0</v>
@@ -6923,8 +6923,8 @@
       <c r="Z64" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA64" s="10" t="n">
-        <v>1</v>
+      <c r="AA64" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -6939,11 +6939,11 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>9474</v>
+        <v>87</v>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>At The River's Edge Club</t>
+          <t>AAA Towsters</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
@@ -6961,13 +6961,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J65" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L65" s="7" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         <v>0</v>
       </c>
       <c r="S65" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T65" s="9" t="n">
         <v>0</v>
@@ -7006,13 +7006,13 @@
         <v>0</v>
       </c>
       <c r="V65" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X65" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y65" s="9" t="n">
         <v>0</v>
@@ -7036,11 +7036,11 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>7450</v>
+        <v>9474</v>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Noon Talkers</t>
+          <t>At The River's Edge Club</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
@@ -7058,13 +7058,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="P66" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q66" s="9" t="n">
         <v>0</v>
@@ -7109,7 +7109,7 @@
         <v>0</v>
       </c>
       <c r="X66" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y66" s="9" t="n">
         <v>0</v>
@@ -7133,15 +7133,15 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>28677953</v>
+        <v>7450</v>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Walsh Toastmasters</t>
+          <t>Noon Talkers</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" s="6" t="n">
         <v>10</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>-27</v>
+        <v>-5</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7182,7 +7182,7 @@
         </is>
       </c>
       <c r="P67" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q67" s="9" t="n">
         <v>0</v>
@@ -7205,14 +7205,14 @@
       <c r="W67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X67" s="9" t="n">
-        <v>0</v>
+      <c r="X67" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z67" s="9" t="n">
-        <v>0</v>
+      <c r="Z67" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA67" s="10" t="n">
         <v>1</v>
@@ -7230,15 +7230,15 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>6570266</v>
+        <v>28677953</v>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Yammertime</t>
+          <t>Walsh Toastmasters</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F68" s="6" t="n">
         <v>10</v>
@@ -7252,13 +7252,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>-2</v>
+        <v>-27</v>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
@@ -7297,19 +7297,19 @@
         <v>0</v>
       </c>
       <c r="V68" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X68" s="10" t="n">
-        <v>6</v>
+      <c r="X68" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z68" s="10" t="n">
-        <v>1</v>
+      <c r="Z68" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA68" s="10" t="n">
         <v>1</v>
@@ -7323,15 +7323,15 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>35</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>4287</v>
+        <v>6570266</v>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>4287 Portland NoonTime Club</t>
+          <t>Yammertime</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
@@ -7349,10 +7349,10 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="K69" s="4" t="n">
         <v>-2</v>
@@ -7399,8 +7399,8 @@
       <c r="W69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X69" s="9" t="n">
-        <v>2</v>
+      <c r="X69" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y69" s="9" t="n">
         <v>0</v>
@@ -7424,11 +7424,11 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>1467</v>
+        <v>4287</v>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Arlington Toastmasters Club</t>
+          <t>4287 Portland NoonTime Club</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
@@ -7446,17 +7446,17 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L70" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L70" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M70" s="8" t="n">
@@ -7491,13 +7491,13 @@
         <v>0</v>
       </c>
       <c r="V70" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W70" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X70" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y70" s="9" t="n">
         <v>0</v>
@@ -7521,15 +7521,15 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>3964</v>
+        <v>1467</v>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Electric Toasters Club</t>
+          <t>Arlington Toastmasters Club</t>
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>10</v>
@@ -7543,17 +7543,17 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>1</v>
+        <v>46</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L71" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L71" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M71" s="8" t="n">
@@ -7588,19 +7588,19 @@
         <v>0</v>
       </c>
       <c r="V71" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W71" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X71" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y71" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z71" s="9" t="n">
-        <v>0</v>
+      <c r="Z71" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA71" s="10" t="n">
         <v>1</v>
@@ -7618,15 +7618,15 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>2978</v>
+        <v>3964</v>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Portlandia Club</t>
+          <t>Electric Toasters Club</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -7640,13 +7640,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="J72" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
@@ -7667,7 +7667,7 @@
         </is>
       </c>
       <c r="P72" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q72" s="9" t="n">
         <v>0</v>
@@ -7685,19 +7685,19 @@
         <v>0</v>
       </c>
       <c r="V72" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X72" s="10" t="n">
-        <v>6</v>
+      <c r="X72" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z72" s="10" t="n">
-        <v>1</v>
+      <c r="Z72" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA72" s="10" t="n">
         <v>1</v>
@@ -7715,15 +7715,15 @@
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>1492</v>
+        <v>2978</v>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Sunrise Toastmasters Club #1492</t>
+          <t>Portlandia Club</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -7737,13 +7737,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>-8</v>
+        <v>-1</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -7751,11 +7751,11 @@
         </is>
       </c>
       <c r="M73" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N73" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O73" s="7" t="inlineStr">
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="P73" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q73" s="9" t="n">
         <v>0</v>
@@ -7782,41 +7782,41 @@
         <v>0</v>
       </c>
       <c r="V73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X73" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z73" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA73" s="9" t="n">
-        <v>0</v>
+      <c r="Z73" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA73" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>959680</v>
+        <v>1492</v>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Banfield Barkers</t>
+          <t>Sunrise Toastmasters Club #1492</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
@@ -7848,11 +7848,11 @@
         </is>
       </c>
       <c r="M74" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N74" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O74" s="7" t="inlineStr">
@@ -7879,7 +7879,7 @@
         <v>0</v>
       </c>
       <c r="V74" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
@@ -7893,8 +7893,8 @@
       <c r="Z74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="AA74" s="10" t="n">
-        <v>1</v>
+      <c r="AA74" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -7909,11 +7909,11 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>701</v>
+        <v>959680</v>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Hood River Club</t>
+          <t>Banfield Barkers</t>
         </is>
       </c>
       <c r="E75" s="5" t="n">
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -7982,7 +7982,7 @@
         <v>0</v>
       </c>
       <c r="X75" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y75" s="9" t="n">
         <v>0</v>
@@ -8006,15 +8006,15 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>3091</v>
+        <v>701</v>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Professionally Speaking</t>
+          <t>Hood River Club</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8028,17 +8028,17 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="K76" s="4" t="n">
         <v>-2</v>
       </c>
-      <c r="L76" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L76" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M76" s="8" t="n">
@@ -8055,10 +8055,10 @@
         </is>
       </c>
       <c r="P76" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q76" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R76" s="9" t="n">
         <v>0</v>
@@ -8066,14 +8066,14 @@
       <c r="S76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T76" s="10" t="n">
-        <v>1</v>
+      <c r="T76" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U76" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V76" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -8084,8 +8084,8 @@
       <c r="Y76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z76" s="10" t="n">
-        <v>1</v>
+      <c r="Z76" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA76" s="10" t="n">
         <v>1</v>
@@ -8103,15 +8103,15 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>9777</v>
+        <v>3091</v>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>The Dalles Toastmasters Club</t>
+          <t>Professionally Speaking</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8125,17 +8125,17 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L77" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-2</v>
+      </c>
+      <c r="L77" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M77" s="8" t="n">
@@ -8152,7 +8152,7 @@
         </is>
       </c>
       <c r="P77" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q77" s="9" t="n">
         <v>1</v>
@@ -8163,20 +8163,20 @@
       <c r="S77" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T77" s="9" t="n">
-        <v>0</v>
+      <c r="T77" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U77" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V77" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W77" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X77" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y77" s="9" t="n">
         <v>0</v>
@@ -8200,15 +8200,15 @@
         </is>
       </c>
       <c r="C78" s="4" t="n">
-        <v>28675879</v>
+        <v>9777</v>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Toastmonsters</t>
+          <t>The Dalles Toastmasters Club</t>
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8222,13 +8222,13 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J78" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
@@ -8249,10 +8249,10 @@
         </is>
       </c>
       <c r="P78" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q78" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R78" s="9" t="n">
         <v>0</v>
@@ -8267,19 +8267,19 @@
         <v>0</v>
       </c>
       <c r="V78" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X78" s="9" t="n">
-        <v>2</v>
+      <c r="X78" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z78" s="9" t="n">
-        <v>0</v>
+      <c r="Z78" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA78" s="10" t="n">
         <v>1</v>
@@ -8297,15 +8297,15 @@
         </is>
       </c>
       <c r="C79" s="4" t="n">
-        <v>353</v>
+        <v>28675879</v>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>Vancouver Toastmasters Club</t>
+          <t>Toastmonsters</t>
         </is>
       </c>
       <c r="E79" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F79" s="6" t="n">
         <v>10</v>
@@ -8319,13 +8319,13 @@
         </is>
       </c>
       <c r="I79" s="4" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J79" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K79" s="4" t="n">
-        <v>-2</v>
+        <v>-11</v>
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         </is>
       </c>
       <c r="P79" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q79" s="9" t="n">
         <v>0</v>
@@ -8364,19 +8364,19 @@
         <v>0</v>
       </c>
       <c r="V79" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X79" s="10" t="n">
-        <v>6</v>
+      <c r="X79" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y79" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z79" s="10" t="n">
-        <v>1</v>
+      <c r="Z79" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA79" s="10" t="n">
         <v>1</v>
@@ -8390,19 +8390,19 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C80" s="4" t="n">
-        <v>3657</v>
+        <v>353</v>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>Early Words Club</t>
+          <t>Vancouver Toastmasters Club</t>
         </is>
       </c>
       <c r="E80" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F80" s="6" t="n">
         <v>10</v>
@@ -8419,10 +8419,10 @@
         <v>12</v>
       </c>
       <c r="J80" s="4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K80" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L80" s="7" t="inlineStr">
         <is>
@@ -8443,10 +8443,10 @@
         </is>
       </c>
       <c r="P80" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q80" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R80" s="9" t="n">
         <v>0</v>
@@ -8454,20 +8454,20 @@
       <c r="S80" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T80" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U80" s="10" t="n">
-        <v>1</v>
+      <c r="T80" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U80" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V80" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W80" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X80" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y80" s="9" t="n">
         <v>0</v>
@@ -8491,15 +8491,15 @@
         </is>
       </c>
       <c r="C81" s="4" t="n">
-        <v>9235</v>
+        <v>3657</v>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>New Beginnings Toastmasters</t>
+          <t>Early Words Club</t>
         </is>
       </c>
       <c r="E81" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F81" s="6" t="n">
         <v>10</v>
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J81" s="4" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -8540,10 +8540,10 @@
         </is>
       </c>
       <c r="P81" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q81" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R81" s="9" t="n">
         <v>0</v>
@@ -8554,8 +8554,8 @@
       <c r="T81" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U81" s="9" t="n">
-        <v>0</v>
+      <c r="U81" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V81" s="9" t="n">
         <v>0</v>
@@ -8564,7 +8564,7 @@
         <v>0</v>
       </c>
       <c r="X81" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y81" s="9" t="n">
         <v>0</v>
@@ -8588,15 +8588,15 @@
         </is>
       </c>
       <c r="C82" s="4" t="n">
-        <v>3045535</v>
+        <v>9235</v>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>Salmon Speakers</t>
+          <t>New Beginnings Toastmasters</t>
         </is>
       </c>
       <c r="E82" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F82" s="6" t="n">
         <v>10</v>
@@ -8610,13 +8610,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="J82" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="J82" s="4" t="n">
-        <v>8</v>
-      </c>
       <c r="K82" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>1</v>
       </c>
       <c r="Q82" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R82" s="9" t="n">
         <v>0</v>
@@ -8648,20 +8648,20 @@
       <c r="S82" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T82" s="9" t="n">
-        <v>0</v>
+      <c r="T82" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U82" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V82" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W82" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X82" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y82" s="9" t="n">
         <v>0</v>
@@ -8685,11 +8685,11 @@
         </is>
       </c>
       <c r="C83" s="4" t="n">
-        <v>741873</v>
+        <v>3045535</v>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Speakers With Spirit Club</t>
+          <t>Salmon Speakers</t>
         </is>
       </c>
       <c r="E83" s="5" t="n">
@@ -8710,10 +8710,10 @@
         <v>9</v>
       </c>
       <c r="J83" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K83" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="7" t="inlineStr">
         <is>
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="P83" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q83" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R83" s="9" t="n">
         <v>0</v>
@@ -8758,7 +8758,7 @@
         <v>0</v>
       </c>
       <c r="X83" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y83" s="9" t="n">
         <v>0</v>
@@ -8782,15 +8782,15 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>610</v>
+        <v>741873</v>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Totem Pole Club</t>
+          <t>Speakers With Spirit Club</t>
         </is>
       </c>
       <c r="E84" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F84" s="6" t="n">
         <v>10</v>
@@ -8804,13 +8804,13 @@
         </is>
       </c>
       <c r="I84" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J84" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K84" s="4" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
@@ -8849,19 +8849,19 @@
         <v>0</v>
       </c>
       <c r="V84" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W84" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X84" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y84" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z84" s="9" t="n">
-        <v>0</v>
+      <c r="Z84" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA84" s="10" t="n">
         <v>1</v>
@@ -8875,15 +8875,15 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C85" s="4" t="n">
-        <v>7244064</v>
+        <v>610</v>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>3 Stripe Adidas</t>
+          <t>Totem Pole Club</t>
         </is>
       </c>
       <c r="E85" s="5" t="n">
@@ -8904,10 +8904,10 @@
         <v>1</v>
       </c>
       <c r="J85" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>0</v>
       </c>
       <c r="X85" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y85" s="9" t="n">
         <v>0</v>
@@ -8976,15 +8976,15 @@
         </is>
       </c>
       <c r="C86" s="4" t="n">
-        <v>608093</v>
+        <v>7244064</v>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Babble-On Toastmasters Club</t>
+          <t>3 Stripe Adidas</t>
         </is>
       </c>
       <c r="E86" s="5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F86" s="6" t="n">
         <v>10</v>
@@ -8998,17 +8998,17 @@
         </is>
       </c>
       <c r="I86" s="4" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="J86" s="4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="K86" s="4" t="n">
-        <v>-5</v>
-      </c>
-      <c r="L86" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L86" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M86" s="8" t="n">
@@ -9027,35 +9027,35 @@
       <c r="P86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q86" s="10" t="n">
-        <v>2</v>
+      <c r="Q86" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R86" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T86" s="10" t="n">
-        <v>1</v>
+      <c r="T86" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U86" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V86" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W86" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X86" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y86" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z86" s="10" t="n">
-        <v>1</v>
+      <c r="Z86" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA86" s="10" t="n">
         <v>1</v>
@@ -9073,15 +9073,15 @@
         </is>
       </c>
       <c r="C87" s="4" t="n">
-        <v>9527</v>
+        <v>608093</v>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Clark County Toastmasters</t>
+          <t>Babble-On Toastmasters Club</t>
         </is>
       </c>
       <c r="E87" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F87" s="6" t="n">
         <v>10</v>
@@ -9095,67 +9095,67 @@
         </is>
       </c>
       <c r="I87" s="4" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="J87" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="K87" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L87" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M87" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N87" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O87" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P87" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q87" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="K87" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L87" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M87" s="8" t="n">
-        <v>46387</v>
-      </c>
-      <c r="N87" s="4" t="inlineStr">
-        <is>
-          <t>Officer list on time</t>
-        </is>
-      </c>
-      <c r="O87" s="7" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P87" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q87" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T87" s="9" t="n">
-        <v>0</v>
+      <c r="T87" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U87" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V87" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X87" s="9" t="n">
-        <v>0</v>
+      <c r="X87" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y87" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z87" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA87" s="9" t="n">
-        <v>0</v>
+      <c r="Z87" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA87" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="88">
@@ -9170,35 +9170,35 @@
         </is>
       </c>
       <c r="C88" s="4" t="n">
-        <v>31</v>
+        <v>9527</v>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Portland Club</t>
+          <t>Clark County Toastmasters</t>
         </is>
       </c>
       <c r="E88" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G88" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I88" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F88" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G88" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H88" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I88" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="J88" s="4" t="n">
-        <v>18</v>
-      </c>
       <c r="K88" s="4" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="L88" s="7" t="inlineStr">
         <is>
@@ -9206,11 +9206,11 @@
         </is>
       </c>
       <c r="M88" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N88" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O88" s="7" t="inlineStr">
@@ -9236,23 +9236,23 @@
       <c r="U88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V88" s="10" t="n">
-        <v>4</v>
+      <c r="V88" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W88" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="X88" s="10" t="n">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="X88" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y88" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z88" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA88" s="10" t="n">
-        <v>1</v>
+      <c r="Z88" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA88" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -9267,11 +9267,11 @@
         </is>
       </c>
       <c r="C89" s="4" t="n">
-        <v>944247</v>
+        <v>31</v>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Rose City Toasters Club</t>
+          <t>Portland Club</t>
         </is>
       </c>
       <c r="E89" s="5" t="n">
@@ -9289,13 +9289,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J89" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -9337,10 +9337,10 @@
         <v>4</v>
       </c>
       <c r="W89" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="X89" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y89" s="9" t="n">
         <v>0</v>
@@ -9364,15 +9364,15 @@
         </is>
       </c>
       <c r="C90" s="4" t="n">
-        <v>1421367</v>
+        <v>944247</v>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Swan Island Toastmasters</t>
+          <t>Rose City Toasters Club</t>
         </is>
       </c>
       <c r="E90" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F90" s="6" t="n">
         <v>10</v>
@@ -9386,13 +9386,13 @@
         </is>
       </c>
       <c r="I90" s="4" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J90" s="4" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="K90" s="4" t="n">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
@@ -9413,7 +9413,7 @@
         </is>
       </c>
       <c r="P90" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q90" s="9" t="n">
         <v>0</v>
@@ -9430,14 +9430,14 @@
       <c r="U90" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V90" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="W90" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X90" s="9" t="n">
-        <v>0</v>
+      <c r="V90" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W90" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="X90" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y90" s="9" t="n">
         <v>0</v>
@@ -9457,19 +9457,19 @@
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>43</t>
         </is>
       </c>
       <c r="C91" s="4" t="n">
-        <v>6222</v>
+        <v>1421367</v>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Civil Tongues Club</t>
+          <t>Swan Island Toastmasters</t>
         </is>
       </c>
       <c r="E91" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91" s="6" t="n">
         <v>10</v>
@@ -9483,13 +9483,13 @@
         </is>
       </c>
       <c r="I91" s="4" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="J91" s="4" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="K91" s="4" t="n">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>1</v>
       </c>
       <c r="Q91" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R91" s="9" t="n">
         <v>0</v>
@@ -9528,19 +9528,19 @@
         <v>0</v>
       </c>
       <c r="V91" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X91" s="10" t="n">
-        <v>7</v>
+      <c r="X91" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y91" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z91" s="9" t="n">
-        <v>0</v>
+      <c r="Z91" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA91" s="10" t="n">
         <v>1</v>
@@ -9558,15 +9558,15 @@
         </is>
       </c>
       <c r="C92" s="4" t="n">
-        <v>783</v>
+        <v>6222</v>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Gresham Toastmasters Club</t>
+          <t>Civil Tongues Club</t>
         </is>
       </c>
       <c r="E92" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F92" s="6" t="n">
         <v>10</v>
@@ -9580,10 +9580,10 @@
         </is>
       </c>
       <c r="I92" s="4" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J92" s="4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K92" s="4" t="n">
         <v>-2</v>
@@ -9610,7 +9610,7 @@
         <v>1</v>
       </c>
       <c r="Q92" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R92" s="9" t="n">
         <v>0</v>
@@ -9625,19 +9625,19 @@
         <v>0</v>
       </c>
       <c r="V92" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W92" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X92" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y92" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z92" s="10" t="n">
-        <v>1</v>
+      <c r="Z92" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA92" s="10" t="n">
         <v>1</v>
@@ -9655,11 +9655,11 @@
         </is>
       </c>
       <c r="C93" s="4" t="n">
-        <v>875188</v>
+        <v>783</v>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Portland Progressives</t>
+          <t>Gresham Toastmasters Club</t>
         </is>
       </c>
       <c r="E93" s="5" t="n">
@@ -9677,10 +9677,10 @@
         </is>
       </c>
       <c r="I93" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J93" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K93" s="4" t="n">
         <v>-2</v>
@@ -9704,7 +9704,7 @@
         </is>
       </c>
       <c r="P93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q93" s="9" t="n">
         <v>0</v>
@@ -9722,13 +9722,13 @@
         <v>0</v>
       </c>
       <c r="V93" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W93" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X93" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y93" s="9" t="n">
         <v>0</v>
@@ -9752,11 +9752,11 @@
         </is>
       </c>
       <c r="C94" s="4" t="n">
-        <v>4999</v>
+        <v>875188</v>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Tabor Toastmasters Club</t>
+          <t>Portland Progressives</t>
         </is>
       </c>
       <c r="E94" s="5" t="n">
@@ -9774,13 +9774,13 @@
         </is>
       </c>
       <c r="I94" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J94" s="4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K94" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
@@ -9819,13 +9819,13 @@
         <v>0</v>
       </c>
       <c r="V94" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W94" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X94" s="9" t="n">
-        <v>3</v>
+      <c r="X94" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y94" s="9" t="n">
         <v>0</v>
@@ -9849,11 +9849,11 @@
         </is>
       </c>
       <c r="C95" s="4" t="n">
-        <v>9521</v>
+        <v>4999</v>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Toastmasters of Portland - Moser Chapter</t>
+          <t>Tabor Toastmasters Club</t>
         </is>
       </c>
       <c r="E95" s="5" t="n">
@@ -9871,13 +9871,13 @@
         </is>
       </c>
       <c r="I95" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J95" s="4" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="K95" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L95" s="7" t="inlineStr">
         <is>
@@ -9921,8 +9921,8 @@
       <c r="W95" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X95" s="10" t="n">
-        <v>7</v>
+      <c r="X95" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y95" s="9" t="n">
         <v>0</v>
@@ -9942,43 +9942,43 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>6643148</v>
+        <v>9521</v>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>CareOregon</t>
+          <t>Toastmasters of Portland - Moser Chapter</t>
         </is>
       </c>
       <c r="E96" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="J96" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="K96" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F96" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G96" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H96" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I96" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="J96" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="K96" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L96" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L96" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M96" s="8" t="n">
@@ -10004,7 +10004,7 @@
         <v>0</v>
       </c>
       <c r="S96" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T96" s="9" t="n">
         <v>0</v>
@@ -10012,14 +10012,14 @@
       <c r="U96" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V96" s="10" t="n">
-        <v>4</v>
+      <c r="V96" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="W96" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X96" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y96" s="9" t="n">
         <v>0</v>
@@ -10043,15 +10043,15 @@
         </is>
       </c>
       <c r="C97" s="4" t="n">
-        <v>2265</v>
+        <v>6643148</v>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Essayons Club</t>
+          <t>CareOregon</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F97" s="6" t="n">
         <v>10</v>
@@ -10065,17 +10065,17 @@
         </is>
       </c>
       <c r="I97" s="4" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="J97" s="4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K97" s="4" t="n">
-        <v>-14</v>
-      </c>
-      <c r="L97" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>1</v>
+      </c>
+      <c r="L97" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M97" s="8" t="n">
@@ -10101,7 +10101,7 @@
         <v>0</v>
       </c>
       <c r="S97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T97" s="9" t="n">
         <v>0</v>
@@ -10109,20 +10109,20 @@
       <c r="U97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V97" s="9" t="n">
-        <v>0</v>
+      <c r="V97" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W97" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X97" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="X97" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y97" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z97" s="9" t="n">
-        <v>0</v>
+      <c r="Z97" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA97" s="10" t="n">
         <v>1</v>
@@ -10140,11 +10140,11 @@
         </is>
       </c>
       <c r="C98" s="4" t="n">
-        <v>28678610</v>
+        <v>2265</v>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>M Financial Toastmasters Club</t>
+          <t>Essayons Club</t>
         </is>
       </c>
       <c r="E98" s="5" t="n">
@@ -10162,13 +10162,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J98" s="4" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>-23</v>
+        <v>-14</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>0</v>
       </c>
       <c r="X98" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y98" s="9" t="n">
         <v>0</v>
@@ -10237,11 +10237,11 @@
         </is>
       </c>
       <c r="C99" s="4" t="n">
-        <v>4993384</v>
+        <v>28678610</v>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Portland Rotary Toastmasters Club</t>
+          <t>M Financial Toastmasters Club</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
@@ -10262,10 +10262,10 @@
         <v>0</v>
       </c>
       <c r="J99" s="4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="K99" s="4" t="n">
-        <v>-27</v>
+        <v>-23</v>
       </c>
       <c r="L99" s="7" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
         <v>0</v>
       </c>
       <c r="X99" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y99" s="9" t="n">
         <v>0</v>
@@ -10325,24 +10325,24 @@
     <row r="100">
       <c r="A100" s="4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>45</t>
         </is>
       </c>
       <c r="C100" s="4" t="n">
-        <v>61</v>
+        <v>4993384</v>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Boise Club</t>
+          <t>Portland Rotary Toastmasters Club</t>
         </is>
       </c>
       <c r="E100" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F100" s="6" t="n">
         <v>10</v>
@@ -10356,13 +10356,13 @@
         </is>
       </c>
       <c r="I100" s="4" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J100" s="4" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K100" s="4" t="n">
-        <v>-4</v>
+        <v>-27</v>
       </c>
       <c r="L100" s="7" t="inlineStr">
         <is>
@@ -10401,19 +10401,19 @@
         <v>0</v>
       </c>
       <c r="V100" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X100" s="10" t="n">
-        <v>5</v>
+      <c r="X100" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y100" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z100" s="10" t="n">
-        <v>1</v>
+      <c r="Z100" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA100" s="10" t="n">
         <v>1</v>
@@ -10431,11 +10431,11 @@
         </is>
       </c>
       <c r="C101" s="4" t="n">
-        <v>5084</v>
+        <v>61</v>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Dynamic Club</t>
+          <t>Boise Club</t>
         </is>
       </c>
       <c r="E101" s="5" t="n">
@@ -10453,13 +10453,13 @@
         </is>
       </c>
       <c r="I101" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J101" s="4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K101" s="4" t="n">
-        <v>1</v>
+        <v>-4</v>
       </c>
       <c r="L101" s="7" t="inlineStr">
         <is>
@@ -10480,16 +10480,16 @@
         </is>
       </c>
       <c r="P101" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R101" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S101" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T101" s="9" t="n">
         <v>0</v>
@@ -10498,7 +10498,7 @@
         <v>0</v>
       </c>
       <c r="V101" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W101" s="9" t="n">
         <v>0</v>
@@ -10528,15 +10528,15 @@
         </is>
       </c>
       <c r="C102" s="4" t="n">
-        <v>1106187</v>
+        <v>5084</v>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Food for Thought</t>
+          <t>Dynamic Club</t>
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F102" s="6" t="n">
         <v>10</v>
@@ -10550,13 +10550,13 @@
         </is>
       </c>
       <c r="I102" s="4" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="J102" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K102" s="4" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="L102" s="7" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
         </is>
       </c>
       <c r="P102" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q102" s="9" t="n">
         <v>0</v>
@@ -10588,20 +10588,20 @@
       <c r="S102" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T102" s="10" t="n">
-        <v>1</v>
+      <c r="T102" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U102" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V102" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W102" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X102" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y102" s="9" t="n">
         <v>0</v>
@@ -10625,15 +10625,15 @@
         </is>
       </c>
       <c r="C103" s="4" t="n">
-        <v>4584188</v>
+        <v>1106187</v>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>River Speakers</t>
+          <t>Food for Thought</t>
         </is>
       </c>
       <c r="E103" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F103" s="6" t="n">
         <v>10</v>
@@ -10647,13 +10647,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J103" s="4" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>-9</v>
+        <v>-4</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -10683,10 +10683,10 @@
         <v>0</v>
       </c>
       <c r="S103" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T103" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T103" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U103" s="9" t="n">
         <v>0</v>
@@ -10697,14 +10697,14 @@
       <c r="W103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X103" s="9" t="n">
-        <v>3</v>
+      <c r="X103" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y103" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z103" s="9" t="n">
-        <v>0</v>
+      <c r="Z103" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA103" s="10" t="n">
         <v>1</v>
@@ -10722,15 +10722,15 @@
         </is>
       </c>
       <c r="C104" s="4" t="n">
-        <v>5279</v>
+        <v>4584188</v>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>The Capitol Club</t>
+          <t>River Speakers</t>
         </is>
       </c>
       <c r="E104" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F104" s="6" t="n">
         <v>10</v>
@@ -10744,13 +10744,13 @@
         </is>
       </c>
       <c r="I104" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="J104" s="4" t="n">
-        <v>13</v>
-      </c>
       <c r="K104" s="4" t="n">
-        <v>-4</v>
+        <v>-9</v>
       </c>
       <c r="L104" s="7" t="inlineStr">
         <is>
@@ -10794,14 +10794,14 @@
       <c r="W104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X104" s="10" t="n">
-        <v>5</v>
+      <c r="X104" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y104" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z104" s="10" t="n">
-        <v>1</v>
+      <c r="Z104" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA104" s="10" t="n">
         <v>1</v>
@@ -10815,15 +10815,15 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C105" s="4" t="n">
-        <v>28678159</v>
+        <v>5279</v>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Capitol Mall Toastmasters</t>
+          <t>The Capitol Club</t>
         </is>
       </c>
       <c r="E105" s="5" t="n">
@@ -10841,10 +10841,10 @@
         </is>
       </c>
       <c r="I105" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J105" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K105" s="4" t="n">
         <v>-4</v>
@@ -10868,7 +10868,7 @@
         </is>
       </c>
       <c r="P105" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q105" s="9" t="n">
         <v>0</v>
@@ -10886,13 +10886,13 @@
         <v>0</v>
       </c>
       <c r="V105" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W105" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X105" s="9" t="n">
-        <v>3</v>
+      <c r="X105" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y105" s="9" t="n">
         <v>0</v>
@@ -10916,11 +10916,11 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>1750</v>
+        <v>28678159</v>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Eclectic Voices Toastmasters</t>
+          <t>Capitol Mall Toastmasters</t>
         </is>
       </c>
       <c r="E106" s="5" t="n">
@@ -10941,10 +10941,10 @@
         <v>11</v>
       </c>
       <c r="J106" s="4" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K106" s="4" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="L106" s="7" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         </is>
       </c>
       <c r="P106" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q106" s="9" t="n">
         <v>0</v>
@@ -10988,8 +10988,8 @@
       <c r="W106" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X106" s="10" t="n">
-        <v>5</v>
+      <c r="X106" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y106" s="9" t="n">
         <v>0</v>
@@ -11013,15 +11013,15 @@
         </is>
       </c>
       <c r="C107" s="4" t="n">
-        <v>2308</v>
+        <v>1750</v>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Pioneer Club</t>
+          <t>Eclectic Voices Toastmasters</t>
         </is>
       </c>
       <c r="E107" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F107" s="6" t="n">
         <v>10</v>
@@ -11035,17 +11035,17 @@
         </is>
       </c>
       <c r="I107" s="4" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="J107" s="4" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="K107" s="4" t="n">
-        <v>-10</v>
-      </c>
-      <c r="L107" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L107" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M107" s="8" t="n">
@@ -11062,7 +11062,7 @@
         </is>
       </c>
       <c r="P107" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q107" s="9" t="n">
         <v>0</v>
@@ -11070,23 +11070,23 @@
       <c r="R107" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S107" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="T107" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U107" s="10" t="n">
-        <v>2</v>
+      <c r="S107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T107" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V107" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W107" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X107" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y107" s="9" t="n">
         <v>0</v>
@@ -11110,15 +11110,15 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>1072821</v>
+        <v>2308</v>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Russet Ramblers</t>
+          <t>Pioneer Club</t>
         </is>
       </c>
       <c r="E108" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F108" s="6" t="n">
         <v>10</v>
@@ -11132,17 +11132,17 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="J108" s="4" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="K108" s="4" t="n">
-        <v>-6</v>
-      </c>
-      <c r="L108" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-9</v>
+      </c>
+      <c r="L108" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M108" s="8" t="n">
@@ -11159,7 +11159,7 @@
         </is>
       </c>
       <c r="P108" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q108" s="9" t="n">
         <v>0</v>
@@ -11167,23 +11167,23 @@
       <c r="R108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T108" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U108" s="9" t="n">
-        <v>0</v>
+      <c r="S108" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="T108" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U108" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V108" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W108" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X108" s="9" t="n">
-        <v>0</v>
+      <c r="X108" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y108" s="9" t="n">
         <v>0</v>
@@ -11207,11 +11207,11 @@
         </is>
       </c>
       <c r="C109" s="4" t="n">
-        <v>149</v>
+        <v>1072821</v>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Twin Falls Toastmasters Club</t>
+          <t>Russet Ramblers</t>
         </is>
       </c>
       <c r="E109" s="5" t="n">
@@ -11232,10 +11232,10 @@
         <v>8</v>
       </c>
       <c r="J109" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K109" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
@@ -11265,7 +11265,7 @@
         <v>0</v>
       </c>
       <c r="S109" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T109" s="9" t="n">
         <v>0</v>
@@ -11274,13 +11274,13 @@
         <v>0</v>
       </c>
       <c r="V109" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W109" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X109" s="10" t="n">
-        <v>7</v>
+      <c r="X109" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y109" s="9" t="n">
         <v>0</v>
@@ -11300,15 +11300,15 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C110" s="4" t="n">
-        <v>28677312</v>
+        <v>149</v>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Chinden Chatterboxes</t>
+          <t>Twin Falls Toastmasters Club</t>
         </is>
       </c>
       <c r="E110" s="5" t="n">
@@ -11353,7 +11353,7 @@
         </is>
       </c>
       <c r="P110" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q110" s="9" t="n">
         <v>0</v>
@@ -11371,7 +11371,7 @@
         <v>0</v>
       </c>
       <c r="V110" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W110" s="9" t="n">
         <v>0</v>
@@ -11401,15 +11401,15 @@
         </is>
       </c>
       <c r="C111" s="4" t="n">
-        <v>1395299</v>
+        <v>28677312</v>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Eagle Toastmasters</t>
+          <t>Chinden Chatterboxes</t>
         </is>
       </c>
       <c r="E111" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F111" s="6" t="n">
         <v>10</v>
@@ -11426,10 +11426,10 @@
         <v>8</v>
       </c>
       <c r="J111" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K111" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L111" s="7" t="inlineStr">
         <is>
@@ -11450,7 +11450,7 @@
         </is>
       </c>
       <c r="P111" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q111" s="9" t="n">
         <v>0</v>
@@ -11459,7 +11459,7 @@
         <v>0</v>
       </c>
       <c r="S111" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T111" s="9" t="n">
         <v>0</v>
@@ -11468,19 +11468,19 @@
         <v>0</v>
       </c>
       <c r="V111" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X111" s="9" t="n">
-        <v>3</v>
+      <c r="X111" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y111" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z111" s="9" t="n">
-        <v>0</v>
+      <c r="Z111" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA111" s="10" t="n">
         <v>1</v>
@@ -11498,15 +11498,15 @@
         </is>
       </c>
       <c r="C112" s="4" t="n">
-        <v>4427</v>
+        <v>1395299</v>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>HP Speakeasies Club</t>
+          <t>Eagle Toastmasters</t>
         </is>
       </c>
       <c r="E112" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F112" s="6" t="n">
         <v>10</v>
@@ -11520,13 +11520,13 @@
         </is>
       </c>
       <c r="I112" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J112" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K112" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L112" s="7" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>0</v>
       </c>
       <c r="S112" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T112" s="9" t="n">
         <v>0</v>
@@ -11565,19 +11565,19 @@
         <v>0</v>
       </c>
       <c r="V112" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W112" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X112" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="W112" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X112" s="10" t="n">
-        <v>6</v>
-      </c>
       <c r="Y112" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z112" s="10" t="n">
-        <v>1</v>
+      <c r="Z112" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA112" s="10" t="n">
         <v>1</v>
@@ -11595,11 +11595,11 @@
         </is>
       </c>
       <c r="C113" s="4" t="n">
-        <v>3497</v>
+        <v>4427</v>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Meridian Club</t>
+          <t>HP Speakeasies Club</t>
         </is>
       </c>
       <c r="E113" s="5" t="n">
@@ -11617,13 +11617,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J113" s="4" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>-12</v>
+        <v>1</v>
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
@@ -11644,16 +11644,16 @@
         </is>
       </c>
       <c r="P113" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q113" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R113" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S113" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T113" s="9" t="n">
         <v>0</v>
@@ -11668,7 +11668,7 @@
         <v>0</v>
       </c>
       <c r="X113" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y113" s="9" t="n">
         <v>0</v>
@@ -11692,15 +11692,15 @@
         </is>
       </c>
       <c r="C114" s="4" t="n">
-        <v>5398</v>
+        <v>3497</v>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Snake River Toastmasters Club #5398</t>
+          <t>Meridian Club</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F114" s="6" t="n">
         <v>10</v>
@@ -11714,67 +11714,67 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="J114" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="K114" s="4" t="n">
+        <v>-12</v>
+      </c>
+      <c r="L114" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="M114" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N114" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O114" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P114" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q114" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U114" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V114" s="9" t="n">
         <v>3</v>
       </c>
-      <c r="J114" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="K114" s="4" t="n">
-        <v>-4</v>
-      </c>
-      <c r="L114" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="M114" s="8" t="n">
-        <v>46387</v>
-      </c>
-      <c r="N114" s="4" t="inlineStr">
-        <is>
-          <t>Officer list on time</t>
-        </is>
-      </c>
-      <c r="O114" s="7" t="inlineStr">
-        <is>
-          <t>not yet</t>
-        </is>
-      </c>
-      <c r="P114" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q114" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R114" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S114" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T114" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U114" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V114" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="W114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X114" s="9" t="n">
-        <v>0</v>
+      <c r="X114" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y114" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z114" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA114" s="9" t="n">
-        <v>0</v>
+      <c r="Z114" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA114" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -11789,15 +11789,15 @@
         </is>
       </c>
       <c r="C115" s="4" t="n">
-        <v>28676088</v>
+        <v>5398</v>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Well Said</t>
+          <t>Snake River Toastmasters Club #5398</t>
         </is>
       </c>
       <c r="E115" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F115" s="6" t="n">
         <v>10</v>
@@ -11811,10 +11811,10 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J115" s="4" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="K115" s="4" t="n">
         <v>-4</v>
@@ -11825,11 +11825,11 @@
         </is>
       </c>
       <c r="M115" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N115" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O115" s="7" t="inlineStr">
@@ -11838,7 +11838,7 @@
         </is>
       </c>
       <c r="P115" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q115" s="9" t="n">
         <v>0</v>
@@ -11856,22 +11856,22 @@
         <v>0</v>
       </c>
       <c r="V115" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X115" s="10" t="n">
-        <v>7</v>
+      <c r="X115" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y115" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z115" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA115" s="10" t="n">
-        <v>1</v>
+      <c r="Z115" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA115" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -11882,19 +11882,19 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>53</t>
         </is>
       </c>
       <c r="C116" s="4" t="n">
-        <v>548</v>
+        <v>28676088</v>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Idaho Falls Club</t>
+          <t>Well Said</t>
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -11908,10 +11908,10 @@
         </is>
       </c>
       <c r="I116" s="4" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J116" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K116" s="4" t="n">
         <v>-4</v>
@@ -11922,11 +11922,11 @@
         </is>
       </c>
       <c r="M116" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N116" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O116" s="7" t="inlineStr">
@@ -11935,7 +11935,7 @@
         </is>
       </c>
       <c r="P116" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q116" s="9" t="n">
         <v>0</v>
@@ -11953,22 +11953,22 @@
         <v>0</v>
       </c>
       <c r="V116" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X116" s="9" t="n">
-        <v>1</v>
+      <c r="X116" s="10" t="n">
+        <v>7</v>
       </c>
       <c r="Y116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z116" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA116" s="9" t="n">
-        <v>0</v>
+      <c r="Z116" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA116" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -11983,15 +11983,15 @@
         </is>
       </c>
       <c r="C117" s="4" t="n">
-        <v>2094512</v>
+        <v>548</v>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Idaho National Laboratory Initiators</t>
+          <t>Idaho Falls Club</t>
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F117" s="6" t="n">
         <v>10</v>
@@ -12005,13 +12005,13 @@
         </is>
       </c>
       <c r="I117" s="4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J117" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K117" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
@@ -12019,11 +12019,11 @@
         </is>
       </c>
       <c r="M117" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N117" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O117" s="7" t="inlineStr">
@@ -12050,7 +12050,7 @@
         <v>0</v>
       </c>
       <c r="V117" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W117" s="9" t="n">
         <v>0</v>
@@ -12061,11 +12061,11 @@
       <c r="Y117" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z117" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA117" s="10" t="n">
-        <v>1</v>
+      <c r="Z117" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA117" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -12080,11 +12080,11 @@
         </is>
       </c>
       <c r="C118" s="4" t="n">
-        <v>1489</v>
+        <v>2094512</v>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Jack C High Club</t>
+          <t>Idaho National Laboratory Initiators</t>
         </is>
       </c>
       <c r="E118" s="5" t="n">
@@ -12102,13 +12102,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="J118" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
@@ -12129,10 +12129,10 @@
         </is>
       </c>
       <c r="P118" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q118" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R118" s="9" t="n">
         <v>0</v>
@@ -12147,13 +12147,13 @@
         <v>0</v>
       </c>
       <c r="V118" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W118" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X118" s="10" t="n">
-        <v>4</v>
+      <c r="X118" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y118" s="9" t="n">
         <v>0</v>
@@ -12177,15 +12177,15 @@
         </is>
       </c>
       <c r="C119" s="4" t="n">
-        <v>7780789</v>
+        <v>1489</v>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>NRF Toastmasters</t>
+          <t>Jack C High Club</t>
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F119" s="6" t="n">
         <v>10</v>
@@ -12199,10 +12199,10 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J119" s="4" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K119" s="4" t="n">
         <v>-2</v>
@@ -12226,10 +12226,10 @@
         </is>
       </c>
       <c r="P119" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q119" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="Q119" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R119" s="9" t="n">
         <v>0</v>
@@ -12244,13 +12244,13 @@
         <v>0</v>
       </c>
       <c r="V119" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W119" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X119" s="9" t="n">
-        <v>0</v>
+      <c r="X119" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y119" s="9" t="n">
         <v>0</v>
@@ -12274,11 +12274,11 @@
         </is>
       </c>
       <c r="C120" s="4" t="n">
-        <v>648473</v>
+        <v>7780789</v>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Smile Toastmasters Club</t>
+          <t>NRF Toastmasters</t>
         </is>
       </c>
       <c r="E120" s="5" t="n">
@@ -12296,10 +12296,10 @@
         </is>
       </c>
       <c r="I120" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J120" s="4" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="K120" s="4" t="n">
         <v>-2</v>
@@ -12347,7 +12347,7 @@
         <v>0</v>
       </c>
       <c r="X120" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y120" s="9" t="n">
         <v>0</v>
@@ -12371,15 +12371,15 @@
         </is>
       </c>
       <c r="C121" s="4" t="n">
-        <v>5480984</v>
+        <v>648473</v>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Strong Women's Legacy</t>
+          <t>Smile Toastmasters Club</t>
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F121" s="6" t="n">
         <v>10</v>
@@ -12393,13 +12393,13 @@
         </is>
       </c>
       <c r="I121" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J121" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K121" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
@@ -12449,8 +12449,8 @@
       <c r="Y121" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z121" s="9" t="n">
-        <v>0</v>
+      <c r="Z121" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA121" s="10" t="n">
         <v>1</v>
@@ -12459,20 +12459,20 @@
     <row r="122">
       <c r="A122" s="4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>54</t>
         </is>
       </c>
       <c r="C122" s="4" t="n">
-        <v>794</v>
+        <v>5480984</v>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Box Elder Club</t>
+          <t>Strong Women's Legacy</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">
@@ -12490,13 +12490,13 @@
         </is>
       </c>
       <c r="I122" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J122" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K122" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L122" s="7" t="inlineStr">
         <is>
@@ -12541,7 +12541,7 @@
         <v>0</v>
       </c>
       <c r="X122" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y122" s="9" t="n">
         <v>0</v>
@@ -12565,15 +12565,15 @@
         </is>
       </c>
       <c r="C123" s="4" t="n">
-        <v>5347188</v>
+        <v>794</v>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Cache Valley Toastmasters</t>
+          <t>Box Elder Club</t>
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F123" s="6" t="n">
         <v>10</v>
@@ -12590,10 +12590,10 @@
         <v>9</v>
       </c>
       <c r="J123" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K123" s="4" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="L123" s="7" t="inlineStr">
         <is>
@@ -12614,7 +12614,7 @@
         </is>
       </c>
       <c r="P123" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q123" s="9" t="n">
         <v>0</v>
@@ -12623,28 +12623,28 @@
         <v>0</v>
       </c>
       <c r="S123" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T123" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T123" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U123" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V123" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X123" s="10" t="n">
-        <v>4</v>
+      <c r="X123" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y123" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z123" s="10" t="n">
-        <v>1</v>
+      <c r="Z123" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA123" s="10" t="n">
         <v>1</v>
@@ -12662,15 +12662,15 @@
         </is>
       </c>
       <c r="C124" s="4" t="n">
-        <v>3531</v>
+        <v>5347188</v>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>I Express Toastmasters Club</t>
+          <t>Cache Valley Toastmasters</t>
         </is>
       </c>
       <c r="E124" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F124" s="6" t="n">
         <v>10</v>
@@ -12684,13 +12684,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J124" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -12711,7 +12711,7 @@
         </is>
       </c>
       <c r="P124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q124" s="9" t="n">
         <v>0</v>
@@ -12720,28 +12720,28 @@
         <v>0</v>
       </c>
       <c r="S124" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T124" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V124" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W124" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X124" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y124" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z124" s="9" t="n">
-        <v>0</v>
+      <c r="Z124" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA124" s="10" t="n">
         <v>1</v>
@@ -12759,15 +12759,15 @@
         </is>
       </c>
       <c r="C125" s="4" t="n">
-        <v>1166333</v>
+        <v>3531</v>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Twilight Toastmasters</t>
+          <t>I Express Toastmasters Club</t>
         </is>
       </c>
       <c r="E125" s="5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F125" s="6" t="n">
         <v>10</v>
@@ -12781,13 +12781,13 @@
         </is>
       </c>
       <c r="I125" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J125" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K125" s="4" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
@@ -12817,10 +12817,10 @@
         <v>0</v>
       </c>
       <c r="S125" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T125" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T125" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U125" s="9" t="n">
         <v>0</v>
@@ -12832,13 +12832,13 @@
         <v>0</v>
       </c>
       <c r="X125" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y125" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z125" s="10" t="n">
-        <v>1</v>
+      <c r="Z125" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA125" s="10" t="n">
         <v>1</v>
@@ -12856,15 +12856,15 @@
         </is>
       </c>
       <c r="C126" s="4" t="n">
-        <v>7156</v>
+        <v>1166333</v>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Wildcat Toastmasters Club</t>
+          <t>Twilight Toastmasters</t>
         </is>
       </c>
       <c r="E126" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F126" s="6" t="n">
         <v>10</v>
@@ -12878,13 +12878,13 @@
         </is>
       </c>
       <c r="I126" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J126" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K126" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L126" s="7" t="inlineStr">
         <is>
@@ -12908,16 +12908,16 @@
         <v>0</v>
       </c>
       <c r="Q126" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R126" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S126" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T126" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T126" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U126" s="9" t="n">
         <v>0</v>
@@ -12929,7 +12929,7 @@
         <v>0</v>
       </c>
       <c r="X126" s="10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y126" s="9" t="n">
         <v>0</v>
@@ -12949,15 +12949,15 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="C127" s="4" t="n">
-        <v>4846</v>
+        <v>7156</v>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Hill Climbers</t>
+          <t>Wildcat Toastmasters Club</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
@@ -12975,13 +12975,13 @@
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J127" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K127" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
@@ -13005,7 +13005,7 @@
         <v>0</v>
       </c>
       <c r="Q127" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R127" s="9" t="n">
         <v>0</v>
@@ -13026,7 +13026,7 @@
         <v>0</v>
       </c>
       <c r="X127" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y127" s="9" t="n">
         <v>0</v>
@@ -13050,15 +13050,15 @@
         </is>
       </c>
       <c r="C128" s="4" t="n">
-        <v>6820</v>
+        <v>4846</v>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Leadership Pathways Toastmasters</t>
+          <t>Hill Climbers</t>
         </is>
       </c>
       <c r="E128" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F128" s="6" t="n">
         <v>10</v>
@@ -13072,13 +13072,13 @@
         </is>
       </c>
       <c r="I128" s="4" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J128" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K128" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L128" s="7" t="inlineStr">
         <is>
@@ -13117,19 +13117,19 @@
         <v>0</v>
       </c>
       <c r="V128" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W128" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X128" s="10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Y128" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z128" s="9" t="n">
-        <v>0</v>
+      <c r="Z128" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA128" s="10" t="n">
         <v>1</v>
@@ -13147,15 +13147,15 @@
         </is>
       </c>
       <c r="C129" s="4" t="n">
-        <v>7064735</v>
+        <v>6820</v>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>More Toasting. More Doing.</t>
+          <t>Leadership Pathways Toastmasters</t>
         </is>
       </c>
       <c r="E129" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F129" s="6" t="n">
         <v>10</v>
@@ -13169,10 +13169,10 @@
         </is>
       </c>
       <c r="I129" s="4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J129" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K129" s="4" t="n">
         <v>-2</v>
@@ -13225,8 +13225,8 @@
       <c r="Y129" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z129" s="10" t="n">
-        <v>1</v>
+      <c r="Z129" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA129" s="10" t="n">
         <v>1</v>
@@ -13244,11 +13244,11 @@
         </is>
       </c>
       <c r="C130" s="4" t="n">
-        <v>1614</v>
+        <v>7064735</v>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>Mount Ogden Toastmasters Club</t>
+          <t>More Toasting. More Doing.</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
@@ -13266,13 +13266,13 @@
         </is>
       </c>
       <c r="I130" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J130" s="4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K130" s="4" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="L130" s="7" t="inlineStr">
         <is>
@@ -13311,13 +13311,13 @@
         <v>0</v>
       </c>
       <c r="V130" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W130" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X130" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y130" s="9" t="n">
         <v>0</v>
@@ -13341,11 +13341,11 @@
         </is>
       </c>
       <c r="C131" s="4" t="n">
-        <v>6840559</v>
+        <v>1614</v>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>Northrop Grumman Minute Talkers</t>
+          <t>Mount Ogden Toastmasters Club</t>
         </is>
       </c>
       <c r="E131" s="5" t="n">
@@ -13363,13 +13363,13 @@
         </is>
       </c>
       <c r="I131" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J131" s="4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="K131" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L131" s="7" t="inlineStr">
         <is>
@@ -13413,8 +13413,8 @@
       <c r="W131" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X131" s="9" t="n">
-        <v>1</v>
+      <c r="X131" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y131" s="9" t="n">
         <v>0</v>
@@ -13434,19 +13434,19 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>62</t>
         </is>
       </c>
       <c r="C132" s="4" t="n">
-        <v>2439</v>
+        <v>6840559</v>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>Energizers Toastmasters Club</t>
+          <t>Northrop Grumman Minute Talkers</t>
         </is>
       </c>
       <c r="E132" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F132" s="6" t="n">
         <v>10</v>
@@ -13460,13 +13460,13 @@
         </is>
       </c>
       <c r="I132" s="4" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="J132" s="4" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K132" s="4" t="n">
-        <v>-6</v>
+        <v>2</v>
       </c>
       <c r="L132" s="7" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         </is>
       </c>
       <c r="P132" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q132" s="9" t="n">
         <v>0</v>
@@ -13505,19 +13505,19 @@
         <v>0</v>
       </c>
       <c r="V132" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X132" s="10" t="n">
-        <v>7</v>
+      <c r="X132" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="Y132" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z132" s="9" t="n">
-        <v>0</v>
+      <c r="Z132" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA132" s="10" t="n">
         <v>1</v>
@@ -13535,35 +13535,35 @@
         </is>
       </c>
       <c r="C133" s="4" t="n">
-        <v>719</v>
+        <v>2439</v>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Metro Toastmasters Club</t>
+          <t>Energizers Toastmasters Club</t>
         </is>
       </c>
       <c r="E133" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F133" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G133" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H133" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I133" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="F133" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G133" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H133" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I133" s="4" t="n">
-        <v>17</v>
-      </c>
       <c r="J133" s="4" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="K133" s="4" t="n">
-        <v>-9</v>
+        <v>-6</v>
       </c>
       <c r="L133" s="7" t="inlineStr">
         <is>
@@ -13584,10 +13584,10 @@
         </is>
       </c>
       <c r="P133" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q133" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="Q133" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="R133" s="9" t="n">
         <v>0</v>
@@ -13601,11 +13601,11 @@
       <c r="U133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V133" s="10" t="n">
-        <v>4</v>
+      <c r="V133" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W133" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X133" s="10" t="n">
         <v>7</v>
@@ -13613,8 +13613,8 @@
       <c r="Y133" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z133" s="10" t="n">
-        <v>1</v>
+      <c r="Z133" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA133" s="10" t="n">
         <v>1</v>
@@ -13632,15 +13632,15 @@
         </is>
       </c>
       <c r="C134" s="4" t="n">
-        <v>28677375</v>
+        <v>719</v>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Risk Management Mavericks</t>
+          <t>Metro Toastmasters Club</t>
         </is>
       </c>
       <c r="E134" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F134" s="6" t="n">
         <v>10</v>
@@ -13654,13 +13654,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J134" s="4" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="L134" s="7" t="inlineStr">
         <is>
@@ -13681,10 +13681,10 @@
         </is>
       </c>
       <c r="P134" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q134" s="9" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q134" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R134" s="9" t="n">
         <v>0</v>
@@ -13698,14 +13698,14 @@
       <c r="U134" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V134" s="9" t="n">
-        <v>1</v>
+      <c r="V134" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W134" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X134" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y134" s="9" t="n">
         <v>0</v>
@@ -13729,15 +13729,15 @@
         </is>
       </c>
       <c r="C135" s="4" t="n">
-        <v>3738</v>
+        <v>28677375</v>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>TNT Club</t>
+          <t>Risk Management Mavericks</t>
         </is>
       </c>
       <c r="E135" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F135" s="6" t="n">
         <v>10</v>
@@ -13751,10 +13751,10 @@
         </is>
       </c>
       <c r="I135" s="4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J135" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K135" s="4" t="n">
         <v>-5</v>
@@ -13778,7 +13778,7 @@
         </is>
       </c>
       <c r="P135" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q135" s="9" t="n">
         <v>0</v>
@@ -13789,20 +13789,20 @@
       <c r="S135" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T135" s="10" t="n">
-        <v>1</v>
+      <c r="T135" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U135" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V135" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W135" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X135" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y135" s="9" t="n">
         <v>0</v>
@@ -13826,11 +13826,11 @@
         </is>
       </c>
       <c r="C136" s="4" t="n">
-        <v>874598</v>
+        <v>3738</v>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>USANA Toastmasters</t>
+          <t>TNT Club</t>
         </is>
       </c>
       <c r="E136" s="5" t="n">
@@ -13848,13 +13848,13 @@
         </is>
       </c>
       <c r="I136" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="J136" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K136" s="4" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="L136" s="7" t="inlineStr">
         <is>
@@ -13875,10 +13875,10 @@
         </is>
       </c>
       <c r="P136" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q136" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R136" s="9" t="n">
         <v>0</v>
@@ -13892,8 +13892,8 @@
       <c r="U136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V136" s="10" t="n">
-        <v>4</v>
+      <c r="V136" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W136" s="9" t="n">
         <v>0</v>
@@ -13904,8 +13904,8 @@
       <c r="Y136" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z136" s="9" t="n">
-        <v>0</v>
+      <c r="Z136" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA136" s="10" t="n">
         <v>1</v>
@@ -13919,19 +13919,19 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>63</t>
         </is>
       </c>
       <c r="C137" s="4" t="n">
-        <v>6875</v>
+        <v>874598</v>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Image Masters Toastmasters Club</t>
+          <t>USANA Toastmasters</t>
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -13945,17 +13945,17 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="J137" s="4" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>-9</v>
-      </c>
-      <c r="L137" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L137" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M137" s="8" t="n">
@@ -13971,11 +13971,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P137" s="10" t="n">
-        <v>4</v>
+      <c r="P137" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Q137" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R137" s="9" t="n">
         <v>0</v>
@@ -13993,16 +13993,16 @@
         <v>4</v>
       </c>
       <c r="W137" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X137" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y137" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z137" s="10" t="n">
-        <v>1</v>
+      <c r="Z137" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA137" s="10" t="n">
         <v>1</v>
@@ -14020,15 +14020,15 @@
         </is>
       </c>
       <c r="C138" s="4" t="n">
-        <v>1982709</v>
+        <v>6875</v>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Parkway Pontificators</t>
+          <t>Image Masters Toastmasters Club</t>
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14042,17 +14042,17 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="J138" s="4" t="n">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="L138" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-7</v>
+      </c>
+      <c r="L138" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M138" s="8" t="n">
@@ -14068,8 +14068,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P138" s="9" t="n">
-        <v>0</v>
+      <c r="P138" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q138" s="9" t="n">
         <v>0</v>
@@ -14080,20 +14080,20 @@
       <c r="S138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T138" s="9" t="n">
-        <v>0</v>
+      <c r="T138" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U138" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V138" s="9" t="n">
-        <v>1</v>
+      <c r="V138" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W138" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X138" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y138" s="9" t="n">
         <v>0</v>
@@ -14117,15 +14117,15 @@
         </is>
       </c>
       <c r="C139" s="4" t="n">
-        <v>1551</v>
+        <v>1982709</v>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Precision Speakers Club</t>
+          <t>Parkway Pontificators</t>
         </is>
       </c>
       <c r="E139" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F139" s="6" t="n">
         <v>10</v>
@@ -14139,13 +14139,13 @@
         </is>
       </c>
       <c r="I139" s="4" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J139" s="4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="K139" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L139" s="7" t="inlineStr">
         <is>
@@ -14153,11 +14153,11 @@
         </is>
       </c>
       <c r="M139" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N139" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O139" s="7" t="inlineStr">
@@ -14184,22 +14184,22 @@
         <v>0</v>
       </c>
       <c r="V139" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X139" s="9" t="n">
-        <v>0</v>
+      <c r="X139" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y139" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z139" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA139" s="9" t="n">
-        <v>0</v>
+      <c r="Z139" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA139" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="140">
@@ -14214,15 +14214,15 @@
         </is>
       </c>
       <c r="C140" s="4" t="n">
-        <v>5396</v>
+        <v>1551</v>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>Salty Tongues Club</t>
+          <t>Precision Speakers Club</t>
         </is>
       </c>
       <c r="E140" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F140" s="6" t="n">
         <v>10</v>
@@ -14236,13 +14236,13 @@
         </is>
       </c>
       <c r="I140" s="4" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J140" s="4" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K140" s="4" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="L140" s="7" t="inlineStr">
         <is>
@@ -14250,11 +14250,11 @@
         </is>
       </c>
       <c r="M140" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N140" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O140" s="7" t="inlineStr">
@@ -14263,10 +14263,10 @@
         </is>
       </c>
       <c r="P140" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q140" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R140" s="9" t="n">
         <v>0</v>
@@ -14281,22 +14281,22 @@
         <v>0</v>
       </c>
       <c r="V140" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X140" s="10" t="n">
-        <v>5</v>
+      <c r="X140" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y140" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z140" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA140" s="10" t="n">
-        <v>1</v>
+      <c r="Z140" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA140" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -14311,11 +14311,11 @@
         </is>
       </c>
       <c r="C141" s="4" t="n">
-        <v>9158</v>
+        <v>5396</v>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Taxmasters Club</t>
+          <t>Salty Tongues Club</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
@@ -14333,10 +14333,10 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J141" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K141" s="4" t="n">
         <v>-3</v>
@@ -14360,7 +14360,7 @@
         </is>
       </c>
       <c r="P141" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q141" s="9" t="n">
         <v>1</v>
@@ -14378,13 +14378,13 @@
         <v>0</v>
       </c>
       <c r="V141" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W141" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X141" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y141" s="9" t="n">
         <v>0</v>
@@ -14404,15 +14404,15 @@
       </c>
       <c r="B142" s="4" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C142" s="4" t="n">
-        <v>6470</v>
+        <v>9158</v>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>Cross-Talkers Club</t>
+          <t>Taxmasters Club</t>
         </is>
       </c>
       <c r="E142" s="5" t="n">
@@ -14430,13 +14430,13 @@
         </is>
       </c>
       <c r="I142" s="4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J142" s="4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K142" s="4" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="L142" s="7" t="inlineStr">
         <is>
@@ -14457,16 +14457,16 @@
         </is>
       </c>
       <c r="P142" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q142" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R142" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S142" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T142" s="9" t="n">
         <v>0</v>
@@ -14475,13 +14475,13 @@
         <v>0</v>
       </c>
       <c r="V142" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W142" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X142" s="10" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y142" s="9" t="n">
         <v>0</v>
@@ -14505,15 +14505,15 @@
         </is>
       </c>
       <c r="C143" s="4" t="n">
-        <v>2410464</v>
+        <v>6470</v>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Lone Peak Toastmasters</t>
+          <t>Cross-Talkers Club</t>
         </is>
       </c>
       <c r="E143" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F143" s="6" t="n">
         <v>10</v>
@@ -14527,17 +14527,17 @@
         </is>
       </c>
       <c r="I143" s="4" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="J143" s="4" t="n">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="K143" s="4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="L143" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L143" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M143" s="8" t="n">
@@ -14554,10 +14554,10 @@
         </is>
       </c>
       <c r="P143" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q143" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R143" s="9" t="n">
         <v>0</v>
@@ -14571,11 +14571,11 @@
       <c r="U143" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V143" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="W143" s="10" t="n">
-        <v>5</v>
+      <c r="V143" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W143" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="X143" s="10" t="n">
         <v>5</v>
@@ -14602,15 +14602,15 @@
         </is>
       </c>
       <c r="C144" s="4" t="n">
-        <v>6782</v>
+        <v>2410464</v>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Park City Toastmasters Club</t>
+          <t>Lone Peak Toastmasters</t>
         </is>
       </c>
       <c r="E144" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F144" s="6" t="n">
         <v>10</v>
@@ -14624,13 +14624,13 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J144" s="4" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="K144" s="4" t="n">
-        <v>-7</v>
+        <v>1</v>
       </c>
       <c r="L144" s="4" t="inlineStr">
         <is>
@@ -14650,8 +14650,8 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P144" s="10" t="n">
-        <v>4</v>
+      <c r="P144" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Q144" s="9" t="n">
         <v>1</v>
@@ -14662,20 +14662,20 @@
       <c r="S144" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T144" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U144" s="10" t="n">
-        <v>1</v>
+      <c r="T144" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U144" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V144" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W144" s="9" t="n">
-        <v>0</v>
+      <c r="W144" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="X144" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y144" s="9" t="n">
         <v>0</v>
@@ -14699,15 +14699,15 @@
         </is>
       </c>
       <c r="C145" s="4" t="n">
-        <v>378</v>
+        <v>6782</v>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Sunrise Toastmasters Club</t>
+          <t>Park City Toastmasters Club</t>
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -14721,17 +14721,17 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="J145" s="4" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L145" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-6</v>
+      </c>
+      <c r="L145" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M145" s="8" t="n">
@@ -14747,11 +14747,11 @@
           <t>not yet</t>
         </is>
       </c>
-      <c r="P145" s="9" t="n">
-        <v>0</v>
+      <c r="P145" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Q145" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R145" s="9" t="n">
         <v>0</v>
@@ -14759,20 +14759,20 @@
       <c r="S145" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T145" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U145" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V145" s="9" t="n">
-        <v>3</v>
+      <c r="T145" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U145" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V145" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W145" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X145" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y145" s="9" t="n">
         <v>0</v>
@@ -14792,19 +14792,19 @@
       </c>
       <c r="B146" s="4" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>65</t>
         </is>
       </c>
       <c r="C146" s="4" t="n">
-        <v>7195</v>
+        <v>378</v>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Olympic Orators Club</t>
+          <t>Sunrise Toastmasters Club</t>
         </is>
       </c>
       <c r="E146" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F146" s="6" t="n">
         <v>10</v>
@@ -14818,17 +14818,17 @@
         </is>
       </c>
       <c r="I146" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J146" s="4" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="K146" s="4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L146" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L146" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M146" s="8" t="n">
@@ -14854,22 +14854,22 @@
         <v>0</v>
       </c>
       <c r="S146" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T146" s="10" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="T146" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U146" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V146" s="10" t="n">
-        <v>4</v>
+      <c r="V146" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="W146" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X146" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y146" s="9" t="n">
         <v>0</v>
@@ -14893,15 +14893,15 @@
         </is>
       </c>
       <c r="C147" s="4" t="n">
-        <v>5892159</v>
+        <v>7195</v>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Silicon Slopes</t>
+          <t>Olympic Orators Club</t>
         </is>
       </c>
       <c r="E147" s="5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F147" s="6" t="n">
         <v>10</v>
@@ -14915,25 +14915,25 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="J147" s="4" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>-3</v>
-      </c>
-      <c r="L147" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-6</v>
+      </c>
+      <c r="L147" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M147" s="8" t="n">
-        <v>46387</v>
+        <v>46446</v>
       </c>
       <c r="N147" s="4" t="inlineStr">
         <is>
-          <t>Officer list on time</t>
+          <t>Officers trained Nov-Feb</t>
         </is>
       </c>
       <c r="O147" s="7" t="inlineStr">
@@ -14953,20 +14953,20 @@
       <c r="S147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T147" s="9" t="n">
-        <v>0</v>
+      <c r="T147" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U147" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V147" s="9" t="n">
+      <c r="V147" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W147" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="W147" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X147" s="9" t="n">
-        <v>0</v>
+      <c r="X147" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y147" s="9" t="n">
         <v>0</v>
@@ -14974,8 +14974,8 @@
       <c r="Z147" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA147" s="9" t="n">
-        <v>0</v>
+      <c r="AA147" s="10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="148">
@@ -14990,15 +14990,15 @@
         </is>
       </c>
       <c r="C148" s="4" t="n">
-        <v>3791</v>
+        <v>5892159</v>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Speaking of Rockets</t>
+          <t>Silicon Slopes</t>
         </is>
       </c>
       <c r="E148" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F148" s="6" t="n">
         <v>10</v>
@@ -15012,13 +15012,13 @@
         </is>
       </c>
       <c r="I148" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J148" s="4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K148" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L148" s="7" t="inlineStr">
         <is>
@@ -15026,11 +15026,11 @@
         </is>
       </c>
       <c r="M148" s="8" t="n">
-        <v>46446</v>
+        <v>46387</v>
       </c>
       <c r="N148" s="4" t="inlineStr">
         <is>
-          <t>Officers trained Nov-Feb</t>
+          <t>Officer list on time</t>
         </is>
       </c>
       <c r="O148" s="7" t="inlineStr">
@@ -15062,8 +15062,8 @@
       <c r="W148" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X148" s="10" t="n">
-        <v>4</v>
+      <c r="X148" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y148" s="9" t="n">
         <v>0</v>
@@ -15071,8 +15071,8 @@
       <c r="Z148" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AA148" s="10" t="n">
-        <v>1</v>
+      <c r="AA148" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -15087,15 +15087,15 @@
         </is>
       </c>
       <c r="C149" s="4" t="n">
-        <v>7391</v>
+        <v>3791</v>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Timpanogos Toastmasters Club</t>
+          <t>Speaking of Rockets</t>
         </is>
       </c>
       <c r="E149" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F149" s="6" t="n">
         <v>10</v>
@@ -15109,13 +15109,13 @@
         </is>
       </c>
       <c r="I149" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J149" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="K149" s="4" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="L149" s="7" t="inlineStr">
         <is>
@@ -15136,7 +15136,7 @@
         </is>
       </c>
       <c r="P149" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q149" s="9" t="n">
         <v>0</v>
@@ -15147,20 +15147,20 @@
       <c r="S149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T149" s="10" t="n">
-        <v>1</v>
+      <c r="T149" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U149" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V149" s="10" t="n">
+      <c r="V149" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="W149" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X149" s="10" t="n">
         <v>4</v>
-      </c>
-      <c r="W149" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="X149" s="10" t="n">
-        <v>6</v>
       </c>
       <c r="Y149" s="9" t="n">
         <v>0</v>
@@ -15184,15 +15184,15 @@
         </is>
       </c>
       <c r="C150" s="4" t="n">
-        <v>7051</v>
+        <v>7391</v>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Utah Valley Club</t>
+          <t>Timpanogos Toastmasters Club</t>
         </is>
       </c>
       <c r="E150" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F150" s="6" t="n">
         <v>10</v>
@@ -15206,17 +15206,17 @@
         </is>
       </c>
       <c r="I150" s="4" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="J150" s="4" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="K150" s="4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L150" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L150" s="7" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M150" s="8" t="n">
@@ -15233,11 +15233,11 @@
         </is>
       </c>
       <c r="P150" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q150" s="10" t="n">
         <v>2</v>
       </c>
+      <c r="Q150" s="9" t="n">
+        <v>0</v>
+      </c>
       <c r="R150" s="9" t="n">
         <v>0</v>
       </c>
@@ -15247,30 +15247,127 @@
       <c r="T150" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U150" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V150" s="9" t="n">
-        <v>0</v>
+      <c r="U150" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V150" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W150" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X150" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y150" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z150" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA150" s="10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="n">
+        <v>7051</v>
+      </c>
+      <c r="D151" s="4" t="inlineStr">
+        <is>
+          <t>Utah Valley Club</t>
+        </is>
+      </c>
+      <c r="E151" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="F151" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G151" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H151" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I151" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J151" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="K151" s="4" t="n">
+        <v>-7</v>
+      </c>
+      <c r="L151" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M151" s="8" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N151" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O151" s="7" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P151" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q151" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R151" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S151" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T151" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U151" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V151" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W151" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X151" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="Y150" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z150" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA150" s="10" t="n">
+      <c r="Y151" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z151" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA151" s="10" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA150"/>
+  <autoFilter ref="A1:AA151"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -15390,13 +15487,13 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5</v>
+        <v>1.83</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -15405,7 +15502,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -15618,25 +15715,25 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -15720,7 +15817,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -15885,7 +15982,7 @@
         <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -16083,7 +16180,7 @@
         <v>6</v>
       </c>
       <c r="D24" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>

--- a/docs/d/207/inyear.xlsx
+++ b/docs/d/207/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:49 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 8 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 8 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 38 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 38 clubs short</t>
         </is>
       </c>
     </row>
@@ -1141,13 +1141,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>4</v>
       </c>
       <c r="W5" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X5" s="9" t="n">
         <v>2</v>
@@ -1238,13 +1238,13 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L6" s="7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1470,8 +1470,8 @@
       <c r="S8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T8" s="9" t="n">
-        <v>0</v>
+      <c r="T8" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U8" s="9" t="n">
         <v>0</v>
@@ -2817,7 +2817,7 @@
         </is>
       </c>
       <c r="P22" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q22" s="9" t="n">
         <v>0</v>
@@ -2890,10 +2890,10 @@
         <v>6</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="L23" s="7" t="inlineStr">
         <is>
@@ -3067,7 +3067,7 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25" s="6" t="n">
         <v>10</v>
@@ -3081,17 +3081,17 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-8</v>
-      </c>
-      <c r="L25" s="7" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-3</v>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M25" s="8" t="n">
@@ -3128,8 +3128,8 @@
       <c r="V25" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W25" s="9" t="n">
-        <v>2</v>
+      <c r="W25" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X25" s="10" t="n">
         <v>6</v>
@@ -3857,13 +3857,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L33" s="7" t="inlineStr">
         <is>
@@ -4245,13 +4245,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L37" s="7" t="inlineStr">
         <is>
@@ -4827,13 +4827,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L43" s="7" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="E46" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" s="6" t="n">
         <v>10</v>
@@ -5118,13 +5118,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L46" s="7" t="inlineStr">
         <is>
@@ -5162,8 +5162,8 @@
       <c r="U46" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V46" s="9" t="n">
-        <v>3</v>
+      <c r="V46" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="L49" s="7" t="inlineStr">
         <is>
@@ -5492,7 +5492,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5535,8 +5535,8 @@
       <c r="P50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Q50" s="9" t="n">
-        <v>1</v>
+      <c r="Q50" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R50" s="9" t="n">
         <v>0</v>
@@ -6282,13 +6282,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L58" s="7" t="inlineStr">
         <is>
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -6705,8 +6705,8 @@
       <c r="R62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S62" s="9" t="n">
-        <v>1</v>
+      <c r="S62" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T62" s="10" t="n">
         <v>1</v>
@@ -7058,13 +7058,13 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="7" t="inlineStr">
         <is>
@@ -7103,7 +7103,7 @@
         <v>0</v>
       </c>
       <c r="V66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W66" s="9" t="n">
         <v>0</v>
@@ -7155,13 +7155,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L67" s="7" t="inlineStr">
         <is>
@@ -7446,13 +7446,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
@@ -7737,13 +7737,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         <v>0</v>
       </c>
       <c r="V73" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>0</v>
@@ -7931,13 +7931,13 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J75" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
@@ -7976,7 +7976,7 @@
         <v>0</v>
       </c>
       <c r="V75" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
@@ -8028,13 +8028,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="L76" s="7" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>0</v>
       </c>
       <c r="V76" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -8111,7 +8111,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8166,8 +8166,8 @@
       <c r="T77" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U77" s="9" t="n">
-        <v>0</v>
+      <c r="U77" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V77" s="9" t="n">
         <v>0</v>
@@ -8513,13 +8513,13 @@
         </is>
       </c>
       <c r="I81" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J81" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K81" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         </is>
       </c>
       <c r="P81" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q81" s="9" t="n">
         <v>1</v>
@@ -8610,13 +8610,13 @@
         </is>
       </c>
       <c r="I82" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J82" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K82" s="4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
@@ -8655,7 +8655,7 @@
         <v>0</v>
       </c>
       <c r="V82" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W82" s="9" t="n">
         <v>0</v>
@@ -8901,13 +8901,13 @@
         </is>
       </c>
       <c r="I85" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J85" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K85" s="4" t="n">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         <v>1</v>
       </c>
       <c r="S87" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T87" s="10" t="n">
         <v>1</v>
@@ -9289,13 +9289,13 @@
         </is>
       </c>
       <c r="I89" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J89" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K89" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L89" s="7" t="inlineStr">
         <is>
@@ -10162,13 +10162,13 @@
         </is>
       </c>
       <c r="I98" s="4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J98" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K98" s="4" t="n">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="L98" s="7" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>0</v>
       </c>
       <c r="S101" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T101" s="9" t="n">
         <v>0</v>
@@ -10647,13 +10647,13 @@
         </is>
       </c>
       <c r="I103" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J103" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K103" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L103" s="7" t="inlineStr">
         <is>
@@ -10692,7 +10692,7 @@
         <v>0</v>
       </c>
       <c r="V103" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W103" s="9" t="n">
         <v>0</v>
@@ -11312,7 +11312,7 @@
         </is>
       </c>
       <c r="E110" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F110" s="6" t="n">
         <v>10</v>
@@ -11364,8 +11364,8 @@
       <c r="S110" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T110" s="9" t="n">
-        <v>0</v>
+      <c r="T110" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U110" s="9" t="n">
         <v>0</v>
@@ -11603,7 +11603,7 @@
         </is>
       </c>
       <c r="E113" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F113" s="6" t="n">
         <v>10</v>
@@ -11617,13 +11617,13 @@
         </is>
       </c>
       <c r="I113" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J113" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K113" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
@@ -11661,8 +11661,8 @@
       <c r="U113" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V113" s="9" t="n">
-        <v>3</v>
+      <c r="V113" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W113" s="9" t="n">
         <v>0</v>
@@ -11714,13 +11714,13 @@
         </is>
       </c>
       <c r="I114" s="4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J114" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K114" s="4" t="n">
-        <v>-12</v>
+        <v>-11</v>
       </c>
       <c r="L114" s="7" t="inlineStr">
         <is>
@@ -11811,13 +11811,13 @@
         </is>
       </c>
       <c r="I115" s="4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J115" s="4" t="n">
         <v>7</v>
       </c>
       <c r="K115" s="4" t="n">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="L115" s="7" t="inlineStr">
         <is>
@@ -11894,7 +11894,7 @@
         </is>
       </c>
       <c r="E116" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F116" s="6" t="n">
         <v>10</v>
@@ -11938,7 +11938,7 @@
         <v>2</v>
       </c>
       <c r="Q116" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R116" s="9" t="n">
         <v>0</v>
@@ -11946,8 +11946,8 @@
       <c r="S116" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T116" s="9" t="n">
-        <v>0</v>
+      <c r="T116" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U116" s="9" t="n">
         <v>0</v>
@@ -12102,13 +12102,13 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J118" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K118" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         </is>
       </c>
       <c r="P119" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q119" s="10" t="n">
         <v>2</v>
@@ -12684,13 +12684,13 @@
         </is>
       </c>
       <c r="I124" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J124" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K124" s="4" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="L124" s="7" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>0</v>
       </c>
       <c r="Q128" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R128" s="9" t="n">
         <v>0</v>
@@ -13654,13 +13654,13 @@
         </is>
       </c>
       <c r="I134" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J134" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K134" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L134" s="7" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         </is>
       </c>
       <c r="E137" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F137" s="6" t="n">
         <v>10</v>
@@ -13945,13 +13945,13 @@
         </is>
       </c>
       <c r="I137" s="4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J137" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K137" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L137" s="7" t="inlineStr">
         <is>
@@ -13986,14 +13986,14 @@
       <c r="T137" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="U137" s="9" t="n">
-        <v>0</v>
+      <c r="U137" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="V137" s="10" t="n">
         <v>4</v>
       </c>
       <c r="W137" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X137" s="10" t="n">
         <v>5</v>
@@ -14028,7 +14028,7 @@
         </is>
       </c>
       <c r="E138" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F138" s="6" t="n">
         <v>10</v>
@@ -14042,13 +14042,13 @@
         </is>
       </c>
       <c r="I138" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J138" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K138" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
         <v>4</v>
       </c>
       <c r="Q138" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R138" s="9" t="n">
         <v>0</v>
@@ -14089,8 +14089,8 @@
       <c r="V138" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W138" s="9" t="n">
-        <v>3</v>
+      <c r="W138" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X138" s="10" t="n">
         <v>6</v>
@@ -14319,7 +14319,7 @@
         </is>
       </c>
       <c r="E141" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F141" s="6" t="n">
         <v>10</v>
@@ -14333,13 +14333,13 @@
         </is>
       </c>
       <c r="I141" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J141" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K141" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L141" s="7" t="inlineStr">
         <is>
@@ -14377,8 +14377,8 @@
       <c r="U141" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V141" s="9" t="n">
-        <v>3</v>
+      <c r="V141" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W141" s="9" t="n">
         <v>0</v>
@@ -14624,10 +14624,10 @@
         </is>
       </c>
       <c r="I144" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="J144" s="4" t="n">
         <v>29</v>
-      </c>
-      <c r="J144" s="4" t="n">
-        <v>28</v>
       </c>
       <c r="K144" s="4" t="n">
         <v>1</v>
@@ -14707,7 +14707,7 @@
         </is>
       </c>
       <c r="E145" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F145" s="6" t="n">
         <v>10</v>
@@ -14721,13 +14721,13 @@
         </is>
       </c>
       <c r="I145" s="4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J145" s="4" t="n">
         <v>34</v>
       </c>
       <c r="K145" s="4" t="n">
-        <v>-6</v>
+        <v>-5</v>
       </c>
       <c r="L145" s="4" t="inlineStr">
         <is>
@@ -14750,8 +14750,8 @@
       <c r="P145" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="Q145" s="9" t="n">
-        <v>1</v>
+      <c r="Q145" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R145" s="9" t="n">
         <v>0</v>
@@ -14845,10 +14845,10 @@
         </is>
       </c>
       <c r="P146" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q146" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R146" s="9" t="n">
         <v>0</v>
@@ -14915,13 +14915,13 @@
         </is>
       </c>
       <c r="I147" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J147" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K147" s="4" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
@@ -14963,7 +14963,7 @@
         <v>4</v>
       </c>
       <c r="W147" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X147" s="10" t="n">
         <v>5</v>
@@ -15487,7 +15487,7 @@
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -15586,7 +15586,7 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -15601,7 +15601,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -15718,7 +15718,7 @@
         <v>5</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -15751,7 +15751,7 @@
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -15817,7 +15817,7 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -15916,7 +15916,7 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>0.67</v>
+        <v>0.83</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -16114,7 +16114,7 @@
         <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -16147,7 +16147,7 @@
         <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -16279,7 +16279,7 @@
         <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -16312,13 +16312,13 @@
         <v>5</v>
       </c>
       <c r="D28" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -16345,7 +16345,7 @@
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
